--- a/database/event/7912/event_7912_evp_summary.xlsx
+++ b/database/event/7912/event_7912_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.5642</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2106</v>
+        <v>3.1379</v>
       </c>
       <c r="E2" t="n">
         <v>8.990500000000001</v>
@@ -548,7 +548,7 @@
         <v>2.4805</v>
       </c>
       <c r="D3" t="n">
-        <v>3.092</v>
+        <v>3.021</v>
       </c>
       <c r="E3" t="n">
         <v>8.696999999999999</v>
@@ -594,7 +594,7 @@
         <v>1.6164</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8681</v>
+        <v>1.814</v>
       </c>
       <c r="E4" t="n">
         <v>5.6674</v>
@@ -640,7 +640,7 @@
         <v>1.4159</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5841</v>
+        <v>1.5339</v>
       </c>
       <c r="E5" t="n">
         <v>4.9643</v>
@@ -686,7 +686,7 @@
         <v>1.1605</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2224</v>
+        <v>1.1772</v>
       </c>
       <c r="E6" t="n">
         <v>4.069</v>
@@ -732,7 +732,7 @@
         <v>0.9056</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8613</v>
+        <v>0.821</v>
       </c>
       <c r="E7" t="n">
         <v>3.1751</v>
@@ -778,7 +778,7 @@
         <v>0.6633</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5182</v>
+        <v>0.4826</v>
       </c>
       <c r="E8" t="n">
         <v>2.3257</v>
@@ -824,7 +824,7 @@
         <v>0.2521</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0643</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="E9" t="n">
         <v>0.8839</v>
@@ -870,7 +870,7 @@
         <v>0.1442</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2171</v>
+        <v>-0.2424</v>
       </c>
       <c r="E10" t="n">
         <v>0.5057</v>
@@ -916,7 +916,7 @@
         <v>0.1316</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.235</v>
+        <v>-0.2601</v>
       </c>
       <c r="E11" t="n">
         <v>0.4614</v>
@@ -962,7 +962,7 @@
         <v>0.0989</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2813</v>
+        <v>-0.3057</v>
       </c>
       <c r="E12" t="n">
         <v>0.3468</v>
@@ -1008,7 +1008,7 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3194</v>
+        <v>-0.3434</v>
       </c>
       <c r="E13" t="n">
         <v>0.2523</v>
@@ -1054,7 +1054,7 @@
         <v>0.0495</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3512</v>
+        <v>-0.3747</v>
       </c>
       <c r="E14" t="n">
         <v>0.1737</v>
@@ -1100,7 +1100,7 @@
         <v>0.0466</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3553</v>
+        <v>-0.3788</v>
       </c>
       <c r="E15" t="n">
         <v>0.1635</v>
@@ -1146,7 +1146,7 @@
         <v>0.0232</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3886</v>
+        <v>-0.4116</v>
       </c>
       <c r="E16" t="n">
         <v>0.08119999999999999</v>
@@ -1192,7 +1192,7 @@
         <v>-0.0124</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4389</v>
+        <v>-0.4612</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0434</v>
@@ -1238,7 +1238,7 @@
         <v>-0.0189</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4482</v>
+        <v>-0.4704</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0664</v>
@@ -1284,7 +1284,7 @@
         <v>-0.0553</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4997</v>
+        <v>-0.5212</v>
       </c>
       <c r="E19" t="n">
         <v>-0.194</v>
@@ -1330,7 +1330,7 @@
         <v>-0.0606</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5072</v>
+        <v>-0.5286</v>
       </c>
       <c r="E20" t="n">
         <v>-0.2126</v>
@@ -1376,7 +1376,7 @@
         <v>-0.09619999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5576</v>
+        <v>-0.5783</v>
       </c>
       <c r="E21" t="n">
         <v>-0.3373</v>
@@ -1422,7 +1422,7 @@
         <v>-0.1149</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.584</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="E22" t="n">
         <v>-0.4027</v>
@@ -1468,7 +1468,7 @@
         <v>-0.1524</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6372</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-0.5343</v>
@@ -1514,7 +1514,7 @@
         <v>-0.1986</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7026</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="E24" t="n">
         <v>-0.6962</v>
@@ -1560,7 +1560,7 @@
         <v>-0.2078</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7157</v>
+        <v>-0.7342</v>
       </c>
       <c r="E25" t="n">
         <v>-0.7286</v>
@@ -1606,7 +1606,7 @@
         <v>-0.2247</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7396</v>
+        <v>-0.7577</v>
       </c>
       <c r="E26" t="n">
         <v>-0.7877</v>
@@ -1652,7 +1652,7 @@
         <v>-0.2337</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7523</v>
+        <v>-0.7703</v>
       </c>
       <c r="E27" t="n">
         <v>-0.8193</v>
@@ -1698,7 +1698,7 @@
         <v>-0.2429</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7655</v>
+        <v>-0.7833</v>
       </c>
       <c r="E28" t="n">
         <v>-0.8518</v>
@@ -1744,7 +1744,7 @@
         <v>-0.3659</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.9396</v>
+        <v>-0.955</v>
       </c>
       <c r="E29" t="n">
         <v>-1.2828</v>
@@ -1790,7 +1790,7 @@
         <v>-0.3708</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E30" t="n">
         <v>-1.3</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3708</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E31" t="n">
         <v>-1.3</v>

--- a/database/event/7912/event_7912_evp_summary.xlsx
+++ b/database/event/7912/event_7912_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.990500000000001</v>
+        <v>8.3292</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5642</v>
+        <v>2.3756</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1379</v>
+        <v>3.1222</v>
       </c>
       <c r="E2" t="n">
-        <v>8.990500000000001</v>
+        <v>8.3292</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.990500000000001</v>
+        <v>8.3292</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9158</v>
+        <v>5.9692</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>189</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9158</v>
+        <v>5.9692</v>
       </c>
       <c r="N2" t="n">
         <v>189</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.696999999999999</v>
+        <v>7.8474</v>
       </c>
       <c r="C3" t="n">
-        <v>2.4805</v>
+        <v>2.2382</v>
       </c>
       <c r="D3" t="n">
-        <v>3.021</v>
+        <v>2.9047</v>
       </c>
       <c r="E3" t="n">
-        <v>8.696999999999999</v>
+        <v>7.8474</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>8.696999999999999</v>
+        <v>7.8474</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6.69</v>
+        <v>5.6239</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>6.69</v>
+        <v>5.6239</v>
       </c>
       <c r="N3" t="n">
         <v>189</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6674</v>
+        <v>5.0508</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6164</v>
+        <v>1.4406</v>
       </c>
       <c r="D4" t="n">
-        <v>1.814</v>
+        <v>1.6422</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6674</v>
+        <v>5.0508</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6674</v>
+        <v>5.0508</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3596</v>
+        <v>3.6197</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>142</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3596</v>
+        <v>3.6197</v>
       </c>
       <c r="N4" t="n">
         <v>142</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9643</v>
+        <v>4.6798</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4159</v>
+        <v>1.3347</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5339</v>
+        <v>1.4747</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9643</v>
+        <v>4.6798</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9643</v>
+        <v>4.6798</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8187</v>
+        <v>3.3538</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>102</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8187</v>
+        <v>3.3538</v>
       </c>
       <c r="N5" t="n">
         <v>102</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.069</v>
+        <v>4.1933</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1605</v>
+        <v>1.196</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1772</v>
+        <v>1.2551</v>
       </c>
       <c r="E6" t="n">
-        <v>4.069</v>
+        <v>4.1933</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.069</v>
+        <v>4.1933</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.13</v>
+        <v>3.0052</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>189</v>
       </c>
       <c r="M6" t="n">
-        <v>3.13</v>
+        <v>3.0052</v>
       </c>
       <c r="N6" t="n">
         <v>189</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1751</v>
+        <v>2.9857</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9056</v>
+        <v>0.8516</v>
       </c>
       <c r="D7" t="n">
-        <v>0.821</v>
+        <v>0.7099</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1751</v>
+        <v>2.9857</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1751</v>
+        <v>2.9857</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4424</v>
+        <v>2.1397</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>142</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4424</v>
+        <v>2.1397</v>
       </c>
       <c r="N7" t="n">
         <v>142</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3257</v>
+        <v>2.2096</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6633</v>
+        <v>0.6302</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4826</v>
+        <v>0.3595</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3257</v>
+        <v>2.2096</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3257</v>
+        <v>2.2096</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.789</v>
+        <v>1.5836</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>189</v>
       </c>
       <c r="M8" t="n">
-        <v>1.789</v>
+        <v>1.5836</v>
       </c>
       <c r="N8" t="n">
         <v>189</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8839</v>
+        <v>1.6649</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2521</v>
+        <v>0.4749</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09180000000000001</v>
+        <v>0.1136</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8839</v>
+        <v>1.6649</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8839</v>
+        <v>1.6649</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6798999999999999</v>
+        <v>1.1932</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>189</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6798999999999999</v>
+        <v>1.1932</v>
       </c>
       <c r="N9" t="n">
         <v>189</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5057</v>
+        <v>0.6878</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1442</v>
+        <v>0.1962</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2424</v>
+        <v>-0.3275</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5057</v>
+        <v>0.6878</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5057</v>
+        <v>0.6878</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.389</v>
+        <v>0.4929</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>102</v>
       </c>
       <c r="M10" t="n">
-        <v>0.389</v>
+        <v>0.4929</v>
       </c>
       <c r="N10" t="n">
         <v>102</v>
@@ -906,26 +906,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4614</v>
+        <v>0.5128</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1316</v>
+        <v>0.1463</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2601</v>
+        <v>-0.4065</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4614</v>
+        <v>0.5128</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4614</v>
+        <v>0.5128</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,44 +934,44 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3549</v>
+        <v>0.3675</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3549</v>
+        <v>0.3675</v>
       </c>
       <c r="N11" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3468</v>
+        <v>0.4648</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0989</v>
+        <v>0.1326</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3057</v>
+        <v>-0.4282</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3468</v>
+        <v>0.4648</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3468</v>
+        <v>0.4648</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2668</v>
+        <v>0.3331</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2668</v>
+        <v>0.3331</v>
       </c>
       <c r="N12" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2523</v>
+        <v>0.4028</v>
       </c>
       <c r="C13" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.1149</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3434</v>
+        <v>-0.4562</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2523</v>
+        <v>0.4028</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2523</v>
+        <v>0.4028</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1941</v>
+        <v>0.2887</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1941</v>
+        <v>0.2887</v>
       </c>
       <c r="N13" t="n">
         <v>61</v>
@@ -1044,26 +1044,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HexT</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1737</v>
+        <v>0.3692</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0495</v>
+        <v>0.1053</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3747</v>
+        <v>-0.4713</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1737</v>
+        <v>0.3692</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1737</v>
+        <v>0.3692</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1336</v>
+        <v>0.2646</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1336</v>
+        <v>0.2646</v>
       </c>
       <c r="N14" t="n">
-        <v>61</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1635</v>
+        <v>0.3349</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0466</v>
+        <v>0.0955</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3788</v>
+        <v>-0.4868</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1635</v>
+        <v>0.3349</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1635</v>
+        <v>0.3349</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1258</v>
+        <v>0.24</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1258</v>
+        <v>0.24</v>
       </c>
       <c r="N15" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>HexT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.1566</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0232</v>
+        <v>0.0447</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4116</v>
+        <v>-0.5673</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.1566</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.1566</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0625</v>
+        <v>0.1122</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0625</v>
+        <v>0.1122</v>
       </c>
       <c r="N16" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.0434</v>
+        <v>0.1313</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0124</v>
+        <v>0.0374</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4612</v>
+        <v>-0.5787</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0434</v>
+        <v>0.1313</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0434</v>
+        <v>0.1313</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0334</v>
+        <v>0.0941</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0334</v>
+        <v>0.0941</v>
       </c>
       <c r="N17" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0664</v>
+        <v>0.1193</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0189</v>
+        <v>0.034</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4704</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0664</v>
+        <v>0.1193</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0664</v>
+        <v>0.1193</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,44 +1256,44 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0511</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0511</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.194</v>
+        <v>0.0756</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0553</v>
+        <v>0.0216</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5212</v>
+        <v>-0.6039</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.194</v>
+        <v>0.0756</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.194</v>
+        <v>0.0756</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1492</v>
+        <v>0.0542</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>52</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1492</v>
+        <v>0.0542</v>
       </c>
       <c r="N19" t="n">
         <v>52</v>
@@ -1320,26 +1320,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2126</v>
+        <v>0.0462</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0606</v>
+        <v>0.0132</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5286</v>
+        <v>-0.6172</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2126</v>
+        <v>0.0462</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2126</v>
+        <v>0.0462</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,44 +1348,44 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1635</v>
+        <v>0.0331</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1635</v>
+        <v>0.0331</v>
       </c>
       <c r="N20" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.3373</v>
+        <v>0.0155</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.0044</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5783</v>
+        <v>-0.631</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3373</v>
+        <v>0.0155</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3373</v>
+        <v>0.0155</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,44 +1394,44 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2595</v>
+        <v>0.0111</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2595</v>
+        <v>0.0111</v>
       </c>
       <c r="N21" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.4027</v>
+        <v>-0.3053</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1149</v>
+        <v>-0.0871</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.7758</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4027</v>
+        <v>-0.3053</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4027</v>
+        <v>-0.3053</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3098</v>
+        <v>-0.2188</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3098</v>
+        <v>-0.2188</v>
       </c>
       <c r="N22" t="n">
-        <v>142</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5343</v>
+        <v>-0.329</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1524</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.7865</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5343</v>
+        <v>-0.329</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5343</v>
+        <v>-0.329</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.411</v>
+        <v>-0.2358</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>36</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.411</v>
+        <v>-0.2358</v>
       </c>
       <c r="N23" t="n">
         <v>36</v>
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.6962</v>
+        <v>-0.5118</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1986</v>
+        <v>-0.146</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.8691</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6962</v>
+        <v>-0.5118</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6962</v>
+        <v>-0.5118</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5355</v>
+        <v>-0.3668</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>52</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5355</v>
+        <v>-0.3668</v>
       </c>
       <c r="N24" t="n">
         <v>52</v>
@@ -1550,26 +1550,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.7286</v>
+        <v>-0.5586</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2078</v>
+        <v>-0.1593</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7342</v>
+        <v>-0.8902</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7286</v>
+        <v>-0.5586</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7286</v>
+        <v>-0.5586</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5605</v>
+        <v>-0.4003</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5605</v>
+        <v>-0.4003</v>
       </c>
       <c r="N25" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7877</v>
+        <v>-0.5774</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2247</v>
+        <v>-0.1647</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7577</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.7877</v>
+        <v>-0.5774</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7877</v>
+        <v>-0.5774</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,19 +1624,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6059</v>
+        <v>-0.4138</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6059</v>
+        <v>-0.4138</v>
       </c>
       <c r="N26" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8193</v>
+        <v>-0.6306</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2337</v>
+        <v>-0.1799</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7703</v>
+        <v>-0.9227</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8193</v>
+        <v>-0.6306</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8193</v>
+        <v>-0.6306</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.6302</v>
+        <v>-0.4519</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6302</v>
+        <v>-0.4519</v>
       </c>
       <c r="N27" t="n">
         <v>36</v>
@@ -1692,22 +1692,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.8518</v>
+        <v>-0.636</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2429</v>
+        <v>-0.1814</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7833</v>
+        <v>-0.9251</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8518</v>
+        <v>-0.636</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.8518</v>
+        <v>-0.636</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6552</v>
+        <v>-0.4558</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>52</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.6552</v>
+        <v>-0.4558</v>
       </c>
       <c r="N28" t="n">
         <v>52</v>
@@ -1734,26 +1734,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.2828</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3659</v>
+        <v>-0.2747</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.955</v>
+        <v>-1.0729</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.2828</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.2828</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9868</v>
+        <v>-0.6903</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.9868</v>
+        <v>-0.6903</v>
       </c>
       <c r="N29" t="n">
-        <v>102</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.3</v>
+        <v>-1.0564</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3708</v>
+        <v>-0.3013</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.9618</v>
+        <v>-1.1149</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.3</v>
+        <v>-1.0564</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.3</v>
+        <v>-1.0564</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,44 +1808,44 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-1</v>
+        <v>-0.7571</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="M30" t="n">
-        <v>-1</v>
+        <v>-0.7571</v>
       </c>
       <c r="N30" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.3</v>
+        <v>-1.2456</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3708</v>
+        <v>-0.3553</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9618</v>
+        <v>-1.2003</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.3</v>
+        <v>-1.2456</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.3</v>
+        <v>-1.2456</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-1</v>
+        <v>-0.8927</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="M31" t="n">
-        <v>-1</v>
+        <v>-0.8927</v>
       </c>
       <c r="N31" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1969,10 +1969,10 @@
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1931</v>
+        <v>0.1767</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0896</v>
+        <v>2.8272</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1723</v>
+        <v>0.1507</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7568</v>
+        <v>2.4112</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0561</v>
+        <v>0.0124</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8976</v>
+        <v>0.1984</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.51</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7242</v>
+        <v>-0.4895</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.5872</v>
+        <v>-7.832</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7608</v>
+        <v>-0.5171</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.1728</v>
+        <v>-8.2736</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2405</v>
+        <v>1.169</v>
       </c>
       <c r="J7" t="n">
-        <v>19.848</v>
+        <v>18.704</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8106</v>
+        <v>0.8923</v>
       </c>
       <c r="J8" t="n">
-        <v>12.9696</v>
+        <v>14.2768</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.34</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7599</v>
+        <v>0.8498</v>
       </c>
       <c r="J9" t="n">
-        <v>12.1584</v>
+        <v>13.5968</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.7841</v>
       </c>
       <c r="J10" t="n">
-        <v>11.008</v>
+        <v>12.5456</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>1.29</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6408</v>
+        <v>0.7392</v>
       </c>
       <c r="J11" t="n">
-        <v>10.2528</v>
+        <v>11.8272</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>2.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.717</v>
+        <v>1.3979</v>
       </c>
       <c r="J12" t="n">
-        <v>32.623</v>
+        <v>26.5601</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.42</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5115</v>
       </c>
       <c r="J13" t="n">
-        <v>10.5621</v>
+        <v>9.718500000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.13</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1448</v>
+        <v>0.1741</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7512</v>
+        <v>3.3079</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.25</v>
+        <v>-0.1359</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.75</v>
+        <v>-2.5821</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.76</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4915</v>
+        <v>-0.3125</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.3385</v>
+        <v>-5.9375</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5725</v>
+        <v>0.5253</v>
       </c>
       <c r="J17" t="n">
-        <v>10.8775</v>
+        <v>9.980700000000001</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4363</v>
+        <v>0.3811</v>
       </c>
       <c r="J18" t="n">
-        <v>8.2897</v>
+        <v>7.2409</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2703</v>
+        <v>-0.1818</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.1357</v>
+        <v>-3.4542</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6334</v>
+        <v>-0.4217</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.0346</v>
+        <v>-8.0123</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.35</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.4382</v>
+        <v>-12.1524</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0762</v>
+        <v>0.987</v>
       </c>
       <c r="J22" t="n">
-        <v>20.4478</v>
+        <v>18.753</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.56</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7205</v>
+        <v>0.6556</v>
       </c>
       <c r="J23" t="n">
-        <v>13.6895</v>
+        <v>12.4564</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.37</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4738</v>
+        <v>0.4584</v>
       </c>
       <c r="J24" t="n">
-        <v>9.0022</v>
+        <v>8.7096</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.11</v>
       </c>
       <c r="I25" t="n">
-        <v>0.112</v>
+        <v>0.145</v>
       </c>
       <c r="J25" t="n">
-        <v>2.128</v>
+        <v>2.755</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.98</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1587</v>
+        <v>-0.0721</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.0153</v>
+        <v>-1.3699</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.92</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0907</v>
+        <v>-0.09</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.7233</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.89</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1446</v>
+        <v>-0.1247</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.7474</v>
+        <v>-2.3693</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2946</v>
+        <v>-0.2071</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.5974</v>
+        <v>-3.9349</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.72</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4447</v>
+        <v>-0.2932</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.449299999999999</v>
+        <v>-5.5708</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4447</v>
+        <v>-0.2932</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.449299999999999</v>
+        <v>-5.5708</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5249</v>
+        <v>0.6197</v>
       </c>
       <c r="J32" t="n">
-        <v>14.6972</v>
+        <v>17.3516</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0828</v>
+        <v>0.0566</v>
       </c>
       <c r="J33" t="n">
-        <v>2.3184</v>
+        <v>1.5848</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.83</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3131</v>
+        <v>-0.1982</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.7668</v>
+        <v>-5.5496</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.72</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4749</v>
+        <v>-0.3066</v>
       </c>
       <c r="J35" t="n">
-        <v>-13.2972</v>
+        <v>-8.5848</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4749</v>
+        <v>-0.3066</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.2972</v>
+        <v>-8.5848</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.57</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3627</v>
+        <v>1.2319</v>
       </c>
       <c r="J37" t="n">
-        <v>38.1556</v>
+        <v>34.4932</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8187</v>
+        <v>0.8182</v>
       </c>
       <c r="J38" t="n">
-        <v>22.9236</v>
+        <v>22.9096</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2682</v>
+        <v>0.3318</v>
       </c>
       <c r="J39" t="n">
-        <v>7.5096</v>
+        <v>9.2904</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.03</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0173</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4844</v>
+        <v>2.408</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.95</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3265</v>
+        <v>-0.2489</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.141999999999999</v>
+        <v>-6.9692</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.01</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0828</v>
+        <v>0.0566</v>
       </c>
       <c r="J42" t="n">
-        <v>1.5732</v>
+        <v>1.0754</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1211</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.3009</v>
+        <v>-1.7537</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2099</v>
+        <v>-0.1358</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.9881</v>
+        <v>-2.5802</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.88</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2285</v>
+        <v>-0.1464</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.3415</v>
+        <v>-2.7816</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2805</v>
+        <v>-0.1777</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.3295</v>
+        <v>-3.3763</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.92</v>
       </c>
       <c r="I47" t="n">
-        <v>1.9437</v>
+        <v>1.6373</v>
       </c>
       <c r="J47" t="n">
-        <v>36.9303</v>
+        <v>31.1087</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.64</v>
       </c>
       <c r="I48" t="n">
-        <v>1.4633</v>
+        <v>1.3012</v>
       </c>
       <c r="J48" t="n">
-        <v>27.8027</v>
+        <v>24.7228</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.26</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6388</v>
+        <v>0.6898</v>
       </c>
       <c r="J49" t="n">
-        <v>12.1372</v>
+        <v>13.1062</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0912</v>
+        <v>0.1691</v>
       </c>
       <c r="J50" t="n">
-        <v>1.7328</v>
+        <v>3.2129</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.43</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.4994</v>
+        <v>-1.5547</v>
       </c>
       <c r="J51" t="n">
-        <v>-28.4886</v>
+        <v>-29.5393</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2078</v>
+        <v>0.1962</v>
       </c>
       <c r="J52" t="n">
-        <v>3.7404</v>
+        <v>3.5316</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0033</v>
+        <v>-0.0272</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0594</v>
+        <v>-0.4896</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1849</v>
+        <v>-0.148</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.3282</v>
+        <v>-2.664</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4336</v>
+        <v>-0.285</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.8048</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.49</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7507</v>
+        <v>-0.5094</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.5126</v>
+        <v>-9.1692</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.87</v>
       </c>
       <c r="I57" t="n">
-        <v>1.7659</v>
+        <v>1.2594</v>
       </c>
       <c r="J57" t="n">
-        <v>31.7862</v>
+        <v>22.6692</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.82</v>
       </c>
       <c r="I58" t="n">
-        <v>1.7066</v>
+        <v>1.2022</v>
       </c>
       <c r="J58" t="n">
-        <v>30.7188</v>
+        <v>21.6396</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.67</v>
       </c>
       <c r="I59" t="n">
-        <v>1.4453</v>
+        <v>1.0283</v>
       </c>
       <c r="J59" t="n">
-        <v>26.0154</v>
+        <v>18.5094</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4177</v>
+        <v>-0.3339</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.5186</v>
+        <v>-6.0102</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.681</v>
+        <v>-0.6186</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.258</v>
+        <v>-11.1348</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>0.84</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1966</v>
+        <v>-0.1669</v>
       </c>
       <c r="J62" t="n">
-        <v>-3.5388</v>
+        <v>-3.0042</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.8</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2628</v>
+        <v>-0.2086</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.7304</v>
+        <v>-3.7548</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.76</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3316</v>
+        <v>-0.2477</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.9688</v>
+        <v>-4.4586</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.74</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3756</v>
+        <v>-0.2658</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.7608</v>
+        <v>-4.7844</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.58</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6188</v>
+        <v>-0.415</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.1384</v>
+        <v>-7.47</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.87</v>
       </c>
       <c r="I67" t="n">
-        <v>1.7788</v>
+        <v>1.2724</v>
       </c>
       <c r="J67" t="n">
-        <v>32.0184</v>
+        <v>22.9032</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.72</v>
       </c>
       <c r="I68" t="n">
-        <v>1.5606</v>
+        <v>1.0975</v>
       </c>
       <c r="J68" t="n">
-        <v>28.0908</v>
+        <v>19.755</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.18</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3769</v>
+        <v>0.4175</v>
       </c>
       <c r="J69" t="n">
-        <v>6.7842</v>
+        <v>7.515</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.13</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2507</v>
+        <v>0.3392</v>
       </c>
       <c r="J70" t="n">
-        <v>4.5126</v>
+        <v>6.1056</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3101</v>
+        <v>-0.2225</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.5818</v>
+        <v>-4.005</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.39</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9774</v>
+        <v>0.7187</v>
       </c>
       <c r="J72" t="n">
-        <v>19.548</v>
+        <v>14.374</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.32</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>16.402</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.27</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6985</v>
+        <v>0.5596</v>
       </c>
       <c r="J74" t="n">
-        <v>13.97</v>
+        <v>11.192</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3052</v>
+        <v>0.3597</v>
       </c>
       <c r="J75" t="n">
-        <v>6.104</v>
+        <v>7.194</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.05</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0706</v>
+        <v>0.1445</v>
       </c>
       <c r="J76" t="n">
-        <v>1.412</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.39</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7096</v>
+        <v>0.6615</v>
       </c>
       <c r="J77" t="n">
-        <v>14.192</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.217</v>
+        <v>0.2065</v>
       </c>
       <c r="J78" t="n">
-        <v>4.34</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.65</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5404</v>
+        <v>-0.3578</v>
       </c>
       <c r="J79" t="n">
-        <v>-10.808</v>
+        <v>-7.156</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.55</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6722</v>
+        <v>-0.4512</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.444</v>
+        <v>-9.023999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9002</v>
+        <v>-0.6252</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.004</v>
+        <v>-12.504</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.56</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3365</v>
+        <v>0.9419</v>
       </c>
       <c r="J82" t="n">
-        <v>28.0665</v>
+        <v>19.7799</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.56</v>
       </c>
       <c r="I83" t="n">
-        <v>1.3365</v>
+        <v>0.9419</v>
       </c>
       <c r="J83" t="n">
-        <v>28.0665</v>
+        <v>19.7799</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.12</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2894</v>
+        <v>0.3465</v>
       </c>
       <c r="J84" t="n">
-        <v>6.0774</v>
+        <v>7.2765</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0678</v>
+        <v>0.0043</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.4238</v>
+        <v>0.09030000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7553</v>
+        <v>-0.7027</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.8613</v>
+        <v>-14.7567</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.31</v>
       </c>
       <c r="I87" t="n">
-        <v>0.58</v>
+        <v>0.5476</v>
       </c>
       <c r="J87" t="n">
-        <v>12.18</v>
+        <v>11.4996</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>0.85</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2604</v>
+        <v>-0.1731</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.4684</v>
+        <v>-3.6351</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2957</v>
+        <v>-0.1932</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.2097</v>
+        <v>-4.0572</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3125</v>
+        <v>-0.2033</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.5625</v>
+        <v>-4.2693</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6983</v>
+        <v>-0.4696</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.6643</v>
+        <v>-9.861599999999999</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>0.91</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.53</v>
+        <v>-1.6434</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.83</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2214</v>
+        <v>-0.1805</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.9852</v>
+        <v>-3.249</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.75</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3702</v>
+        <v>-0.2582</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.6636</v>
+        <v>-4.6476</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.68</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4837</v>
+        <v>-0.3237</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.7066</v>
+        <v>-5.8266</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.63</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5555</v>
+        <v>-0.3707</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.999000000000001</v>
+        <v>-6.6726</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3225</v>
+        <v>0.9376</v>
       </c>
       <c r="J97" t="n">
-        <v>23.805</v>
+        <v>16.8768</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8626</v>
+        <v>0.6593</v>
       </c>
       <c r="J98" t="n">
-        <v>15.5268</v>
+        <v>11.8674</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.29</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7143</v>
+        <v>0.5813</v>
       </c>
       <c r="J99" t="n">
-        <v>12.8574</v>
+        <v>10.4634</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4158</v>
+        <v>0.4299</v>
       </c>
       <c r="J100" t="n">
-        <v>7.4844</v>
+        <v>7.7382</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1494</v>
+        <v>-0.0677</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.6892</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3345</v>
+        <v>0.3568</v>
       </c>
       <c r="J102" t="n">
-        <v>11.373</v>
+        <v>12.1312</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1475</v>
+        <v>0.1455</v>
       </c>
       <c r="J103" t="n">
-        <v>5.015</v>
+        <v>4.947</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.02</v>
+        <v>0.0039</v>
       </c>
       <c r="J104" t="n">
-        <v>0.68</v>
+        <v>0.1326</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2357</v>
+        <v>-0.1421</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.0138</v>
+        <v>-4.8314</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.76</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4338</v>
+        <v>-0.2753</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.7492</v>
+        <v>-9.360200000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.44</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0908</v>
+        <v>0.7864</v>
       </c>
       <c r="J107" t="n">
-        <v>37.0872</v>
+        <v>26.7376</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.44</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0908</v>
+        <v>0.7864</v>
       </c>
       <c r="J108" t="n">
-        <v>37.0872</v>
+        <v>26.7376</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.22</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5709</v>
+        <v>0.4933</v>
       </c>
       <c r="J109" t="n">
-        <v>19.4106</v>
+        <v>16.7722</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.04</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0429</v>
+        <v>0.1148</v>
       </c>
       <c r="J110" t="n">
-        <v>1.4586</v>
+        <v>3.9032</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3343</v>
+        <v>-0.2549</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.3662</v>
+        <v>-8.666600000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9361</v>
+        <v>0.6792</v>
       </c>
       <c r="J112" t="n">
-        <v>21.5303</v>
+        <v>15.6216</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.26</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7526</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>17.3098</v>
+        <v>13.041</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.345</v>
+        <v>0.3419</v>
       </c>
       <c r="J114" t="n">
-        <v>7.935</v>
+        <v>7.8637</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.01</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.022</v>
+        <v>0.0308</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.506</v>
+        <v>0.7084</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.8</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7038</v>
+        <v>-0.6508</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.1874</v>
+        <v>-14.9684</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.18</v>
       </c>
       <c r="I117" t="n">
-        <v>0.378</v>
+        <v>0.3874</v>
       </c>
       <c r="J117" t="n">
-        <v>8.694000000000001</v>
+        <v>8.9102</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.16</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3482</v>
+        <v>0.3647</v>
       </c>
       <c r="J118" t="n">
-        <v>8.008599999999999</v>
+        <v>8.3881</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0469</v>
+        <v>-0.0448</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.0787</v>
+        <v>-1.0304</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3514</v>
+        <v>-0.2211</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.0822</v>
+        <v>-5.0853</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6965</v>
+        <v>-0.4678</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.0195</v>
+        <v>-10.7594</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.16</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3316</v>
+        <v>0.2832</v>
       </c>
       <c r="J122" t="n">
-        <v>7.2952</v>
+        <v>6.2304</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2849</v>
+        <v>0.2387</v>
       </c>
       <c r="J123" t="n">
-        <v>6.2678</v>
+        <v>5.2514</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.99</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0216</v>
+        <v>-0.0194</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.4752</v>
+        <v>-0.4268</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.93</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1666</v>
+        <v>-0.098</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.6652</v>
+        <v>-2.156</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5296</v>
+        <v>-0.3434</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.6512</v>
+        <v>-7.5548</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.49</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7013</v>
+        <v>0.5028</v>
       </c>
       <c r="J127" t="n">
-        <v>15.4286</v>
+        <v>11.0616</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.2</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3239</v>
+        <v>0.2847</v>
       </c>
       <c r="J128" t="n">
-        <v>7.1258</v>
+        <v>6.2634</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.19</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3079</v>
+        <v>0.2725</v>
       </c>
       <c r="J129" t="n">
-        <v>6.7738</v>
+        <v>5.995</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0046</v>
+        <v>0.0284</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.1012</v>
+        <v>0.6248</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.92</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2345</v>
+        <v>-0.129</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.159</v>
+        <v>-2.838</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>2.22</v>
       </c>
       <c r="I132" t="n">
-        <v>2.0744</v>
+        <v>1.6425</v>
       </c>
       <c r="J132" t="n">
-        <v>33.1904</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.5</v>
       </c>
       <c r="I133" t="n">
-        <v>1.092</v>
+        <v>0.8236</v>
       </c>
       <c r="J133" t="n">
-        <v>17.472</v>
+        <v>13.1776</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.48</v>
       </c>
       <c r="I134" t="n">
-        <v>1.0467</v>
+        <v>0.8</v>
       </c>
       <c r="J134" t="n">
-        <v>16.7472</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2521</v>
+        <v>0.3453</v>
       </c>
       <c r="J135" t="n">
-        <v>4.0336</v>
+        <v>5.5248</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3933</v>
+        <v>-0.3077</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.2928</v>
+        <v>-4.9232</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.26</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5501</v>
+        <v>0.5258</v>
       </c>
       <c r="J137" t="n">
-        <v>8.801600000000001</v>
+        <v>8.412800000000001</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1648</v>
+        <v>-0.1416</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.6368</v>
+        <v>-2.2656</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.66</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.5208</v>
+        <v>-0.3458</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.332800000000001</v>
+        <v>-5.5328</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.62</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.217599999999999</v>
+        <v>-6.1344</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.731</v>
+        <v>-0.495</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.696</v>
+        <v>-7.92</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7912/event_7912_evp_summary.xlsx
+++ b/database/event/7912/event_7912_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3292</v>
+        <v>8.1157</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3756</v>
+        <v>2.3147</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1222</v>
+        <v>3.0702</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3292</v>
+        <v>8.1157</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.3292</v>
+        <v>8.1157</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9692</v>
+        <v>6.3795</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>189</v>
       </c>
       <c r="M2" t="n">
-        <v>5.9692</v>
+        <v>6.3795</v>
       </c>
       <c r="N2" t="n">
         <v>189</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8474</v>
+        <v>7.665</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2382</v>
+        <v>2.1862</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9047</v>
+        <v>2.8651</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8474</v>
+        <v>7.665</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8474</v>
+        <v>7.665</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6239</v>
+        <v>6.0252</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6239</v>
+        <v>6.0252</v>
       </c>
       <c r="N3" t="n">
         <v>189</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0508</v>
+        <v>4.9646</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4406</v>
+        <v>1.416</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6422</v>
+        <v>1.6358</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0508</v>
+        <v>4.9646</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0508</v>
+        <v>4.9646</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6197</v>
+        <v>3.9025</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>142</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6197</v>
+        <v>3.9025</v>
       </c>
       <c r="N4" t="n">
         <v>142</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6798</v>
+        <v>4.6574</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3347</v>
+        <v>1.3284</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4747</v>
+        <v>1.4959</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6798</v>
+        <v>4.6574</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6798</v>
+        <v>4.6574</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3538</v>
+        <v>3.661</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>102</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3538</v>
+        <v>3.661</v>
       </c>
       <c r="N5" t="n">
         <v>102</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1933</v>
+        <v>4.0965</v>
       </c>
       <c r="C6" t="n">
-        <v>1.196</v>
+        <v>1.1684</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2551</v>
+        <v>1.2406</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1933</v>
+        <v>4.0965</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1933</v>
+        <v>4.0965</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0052</v>
+        <v>3.2201</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>189</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0052</v>
+        <v>3.2201</v>
       </c>
       <c r="N6" t="n">
         <v>189</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9857</v>
+        <v>2.8426</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8516</v>
+        <v>0.8107</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7099</v>
+        <v>0.6698</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9857</v>
+        <v>2.8426</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9857</v>
+        <v>2.8426</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1397</v>
+        <v>2.2345</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>142</v>
       </c>
       <c r="M7" t="n">
-        <v>2.1397</v>
+        <v>2.2345</v>
       </c>
       <c r="N7" t="n">
         <v>142</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2096</v>
+        <v>2.49</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6302</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3595</v>
+        <v>0.5093</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2096</v>
+        <v>2.49</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2096</v>
+        <v>2.49</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5836</v>
+        <v>1.9573</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>189</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5836</v>
+        <v>1.9573</v>
       </c>
       <c r="N8" t="n">
         <v>189</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.6649</v>
+        <v>1.5893</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4749</v>
+        <v>0.4533</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1136</v>
+        <v>0.0993</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6649</v>
+        <v>1.5893</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6649</v>
+        <v>1.5893</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1932</v>
+        <v>1.2493</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>189</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1932</v>
+        <v>1.2493</v>
       </c>
       <c r="N9" t="n">
         <v>189</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6878</v>
+        <v>0.6974</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1962</v>
+        <v>0.1989</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3275</v>
+        <v>-0.3067</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6878</v>
+        <v>0.6974</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6878</v>
+        <v>0.6974</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4929</v>
+        <v>0.5482</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>102</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4929</v>
+        <v>0.5482</v>
       </c>
       <c r="N10" t="n">
         <v>102</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5128</v>
+        <v>0.4819</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1463</v>
+        <v>0.1374</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4065</v>
+        <v>-0.4048</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5128</v>
+        <v>0.4819</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5128</v>
+        <v>0.4819</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3675</v>
+        <v>0.3788</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>142</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3675</v>
+        <v>0.3788</v>
       </c>
       <c r="N11" t="n">
         <v>142</v>
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4648</v>
+        <v>0.4765</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1326</v>
+        <v>0.1359</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4282</v>
+        <v>-0.4073</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4648</v>
+        <v>0.4765</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4648</v>
+        <v>0.4765</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3331</v>
+        <v>0.3746</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3331</v>
+        <v>0.3746</v>
       </c>
       <c r="N12" t="n">
         <v>61</v>
@@ -998,26 +998,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4028</v>
+        <v>0.4608</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1149</v>
+        <v>0.1314</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4562</v>
+        <v>-0.4144</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4028</v>
+        <v>0.4608</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4028</v>
+        <v>0.4608</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,44 +1026,44 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2887</v>
+        <v>0.3622</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2887</v>
+        <v>0.3622</v>
       </c>
       <c r="N13" t="n">
-        <v>61</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3692</v>
+        <v>0.4053</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1053</v>
+        <v>0.1156</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4713</v>
+        <v>-0.4397</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3692</v>
+        <v>0.4053</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3692</v>
+        <v>0.4053</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,19 +1072,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2646</v>
+        <v>0.3186</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2646</v>
+        <v>0.3186</v>
       </c>
       <c r="N14" t="n">
-        <v>102</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3349</v>
+        <v>0.3582</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0955</v>
+        <v>0.1022</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4868</v>
+        <v>-0.4611</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3349</v>
+        <v>0.3582</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3349</v>
+        <v>0.3582</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.24</v>
+        <v>0.2816</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>142</v>
       </c>
       <c r="M15" t="n">
-        <v>0.24</v>
+        <v>0.2816</v>
       </c>
       <c r="N15" t="n">
         <v>142</v>
@@ -1136,26 +1136,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HexT</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1566</v>
+        <v>0.2969</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0447</v>
+        <v>0.0847</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5673</v>
+        <v>-0.489</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1566</v>
+        <v>0.2969</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1566</v>
+        <v>0.2969</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1122</v>
+        <v>0.2334</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1122</v>
+        <v>0.2334</v>
       </c>
       <c r="N16" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>HexT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1313</v>
+        <v>0.2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0374</v>
+        <v>0.057</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5787</v>
+        <v>-0.5332</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1313</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1313</v>
+        <v>0.2</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0941</v>
+        <v>0.1572</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0941</v>
+        <v>0.1572</v>
       </c>
       <c r="N17" t="n">
         <v>61</v>
@@ -1228,26 +1228,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1193</v>
+        <v>0.1046</v>
       </c>
       <c r="C18" t="n">
-        <v>0.034</v>
+        <v>0.0298</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.5766</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1193</v>
+        <v>0.1046</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1193</v>
+        <v>0.1046</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,44 +1256,44 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0822</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0822</v>
       </c>
       <c r="N18" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0756</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0216</v>
+        <v>0.0209</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6039</v>
+        <v>-0.5908</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0756</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0756</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,44 +1302,44 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0542</v>
+        <v>0.0577</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0542</v>
+        <v>0.0577</v>
       </c>
       <c r="N19" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0462</v>
+        <v>0.0527</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0132</v>
+        <v>0.015</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6172</v>
+        <v>-0.6002</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0462</v>
+        <v>0.0527</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0462</v>
+        <v>0.0527</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0331</v>
+        <v>0.0414</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>52</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0331</v>
+        <v>0.0414</v>
       </c>
       <c r="N20" t="n">
         <v>52</v>
@@ -1366,26 +1366,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0155</v>
+        <v>0.037</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0044</v>
+        <v>0.0106</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.631</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0155</v>
+        <v>0.037</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0155</v>
+        <v>0.037</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,19 +1394,19 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0111</v>
+        <v>0.0291</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0111</v>
+        <v>0.0291</v>
       </c>
       <c r="N21" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3053</v>
+        <v>-0.3049</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0871</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7758</v>
+        <v>-0.763</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3053</v>
+        <v>-0.3049</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3053</v>
+        <v>-0.3049</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2188</v>
+        <v>-0.2397</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>36</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2188</v>
+        <v>-0.2397</v>
       </c>
       <c r="N22" t="n">
         <v>36</v>
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.329</v>
+        <v>-0.343</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0978</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7865</v>
+        <v>-0.7803</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.329</v>
+        <v>-0.343</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.329</v>
+        <v>-0.343</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2358</v>
+        <v>-0.2696</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>36</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2358</v>
+        <v>-0.2696</v>
       </c>
       <c r="N23" t="n">
         <v>36</v>
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.5118</v>
+        <v>-0.4883</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.146</v>
+        <v>-0.1393</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8691</v>
+        <v>-0.8465</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5118</v>
+        <v>-0.4883</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5118</v>
+        <v>-0.4883</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3668</v>
+        <v>-0.3838</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>52</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3668</v>
+        <v>-0.3838</v>
       </c>
       <c r="N24" t="n">
         <v>52</v>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5586</v>
+        <v>-0.5512</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1593</v>
+        <v>-0.1572</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8902</v>
+        <v>-0.8751</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5586</v>
+        <v>-0.5512</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5586</v>
+        <v>-0.5512</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4003</v>
+        <v>-0.4333</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4003</v>
+        <v>-0.4333</v>
       </c>
       <c r="N25" t="n">
         <v>52</v>
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.5774</v>
+        <v>-0.574</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1647</v>
+        <v>-0.1637</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8987000000000001</v>
+        <v>-0.8855</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5774</v>
+        <v>-0.574</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5774</v>
+        <v>-0.574</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4138</v>
+        <v>-0.4512</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4138</v>
+        <v>-0.4512</v>
       </c>
       <c r="N26" t="n">
         <v>36</v>
@@ -1642,26 +1642,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6306</v>
+        <v>-0.6226</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1799</v>
+        <v>-0.1776</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9227</v>
+        <v>-0.9076</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6306</v>
+        <v>-0.6226</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6306</v>
+        <v>-0.6226</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4519</v>
+        <v>-0.4894</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4519</v>
+        <v>-0.4894</v>
       </c>
       <c r="N27" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.636</v>
+        <v>-0.6231</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1814</v>
+        <v>-0.1777</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9251</v>
+        <v>-0.9079</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.636</v>
+        <v>-0.6231</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.636</v>
+        <v>-0.6231</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,19 +1716,19 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4558</v>
+        <v>-0.4898</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4558</v>
+        <v>-0.4898</v>
       </c>
       <c r="N28" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.8772</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2747</v>
+        <v>-0.2502</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0729</v>
+        <v>-1.0235</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.8772</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.8772</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6903</v>
+        <v>-0.6895</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>61</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6903</v>
+        <v>-0.6895</v>
       </c>
       <c r="N29" t="n">
         <v>61</v>
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.0564</v>
+        <v>-0.9972</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3013</v>
+        <v>-0.2844</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1149</v>
+        <v>-1.0781</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.0564</v>
+        <v>-0.9972</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.0564</v>
+        <v>-0.9972</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7571</v>
+        <v>-0.7839</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>36</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7571</v>
+        <v>-0.7839</v>
       </c>
       <c r="N30" t="n">
         <v>36</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.2456</v>
+        <v>-1.0486</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3553</v>
+        <v>-0.2991</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.2003</v>
+        <v>-1.1015</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.2456</v>
+        <v>-1.0486</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.2456</v>
+        <v>-1.0486</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8927</v>
+        <v>-0.8243</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>102</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8927</v>
+        <v>-0.8243</v>
       </c>
       <c r="N31" t="n">
         <v>102</v>
@@ -1969,10 +1969,10 @@
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1767</v>
+        <v>0.1688</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8272</v>
+        <v>2.7008</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1507</v>
+        <v>0.1428</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4112</v>
+        <v>2.2848</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0124</v>
+        <v>-0.0041</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1984</v>
+        <v>-0.06560000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.51</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4895</v>
+        <v>-0.498</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.832</v>
+        <v>-7.968</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5171</v>
+        <v>-0.5238</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.2736</v>
+        <v>-8.380800000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1.169</v>
+        <v>1.1888</v>
       </c>
       <c r="J7" t="n">
-        <v>18.704</v>
+        <v>19.0208</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8923</v>
+        <v>0.8465</v>
       </c>
       <c r="J8" t="n">
-        <v>14.2768</v>
+        <v>13.544</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.34</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8498</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>13.5968</v>
+        <v>12.944</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7841</v>
+        <v>0.751</v>
       </c>
       <c r="J10" t="n">
-        <v>12.5456</v>
+        <v>12.016</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>1.29</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7392</v>
+        <v>0.7114</v>
       </c>
       <c r="J11" t="n">
-        <v>11.8272</v>
+        <v>11.3824</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>2.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3979</v>
+        <v>1.5666</v>
       </c>
       <c r="J12" t="n">
-        <v>26.5601</v>
+        <v>29.7654</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.42</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5115</v>
+        <v>0.5244</v>
       </c>
       <c r="J13" t="n">
-        <v>9.718500000000001</v>
+        <v>9.9636</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.13</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1741</v>
+        <v>0.197</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3079</v>
+        <v>3.743</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1359</v>
+        <v>-0.1395</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.5821</v>
+        <v>-2.6505</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.76</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3125</v>
+        <v>-0.3181</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.9375</v>
+        <v>-6.0439</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5253</v>
+        <v>0.508</v>
       </c>
       <c r="J17" t="n">
-        <v>9.980700000000001</v>
+        <v>9.651999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3811</v>
+        <v>0.3739</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2409</v>
+        <v>7.1041</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1818</v>
+        <v>-0.1991</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.4542</v>
+        <v>-3.7829</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4217</v>
+        <v>-0.4328</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.0123</v>
+        <v>-8.2232</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.35</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.6375</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.1524</v>
+        <v>-12.1125</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.9</v>
       </c>
       <c r="I22" t="n">
-        <v>0.987</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>18.753</v>
+        <v>18.5117</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.56</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6556</v>
+        <v>0.6603</v>
       </c>
       <c r="J23" t="n">
-        <v>12.4564</v>
+        <v>12.5457</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.37</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4584</v>
+        <v>0.4738</v>
       </c>
       <c r="J24" t="n">
-        <v>8.7096</v>
+        <v>9.0022</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.11</v>
       </c>
       <c r="I25" t="n">
-        <v>0.145</v>
+        <v>0.1682</v>
       </c>
       <c r="J25" t="n">
-        <v>2.755</v>
+        <v>3.1958</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.98</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0721</v>
+        <v>-0.0708</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.3699</v>
+        <v>-1.3452</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.92</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.09</v>
+        <v>-0.107</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.71</v>
+        <v>-2.033</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.89</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1247</v>
+        <v>-0.1424</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.3693</v>
+        <v>-2.7056</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2071</v>
+        <v>-0.2255</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.9349</v>
+        <v>-4.2845</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.72</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2932</v>
+        <v>-0.3104</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.5708</v>
+        <v>-5.8976</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2932</v>
+        <v>-0.3104</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.5708</v>
+        <v>-5.8976</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6197</v>
+        <v>0.5933</v>
       </c>
       <c r="J32" t="n">
-        <v>17.3516</v>
+        <v>16.6124</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0566</v>
+        <v>0.0569</v>
       </c>
       <c r="J33" t="n">
-        <v>1.5848</v>
+        <v>1.5932</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.83</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1982</v>
+        <v>-0.2141</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.5496</v>
+        <v>-5.9948</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.72</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3066</v>
+        <v>-0.3208</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.5848</v>
+        <v>-8.9824</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3066</v>
+        <v>-0.3208</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.5848</v>
+        <v>-8.9824</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.57</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2319</v>
+        <v>1.2701</v>
       </c>
       <c r="J37" t="n">
-        <v>34.4932</v>
+        <v>35.5628</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8182</v>
+        <v>0.7743</v>
       </c>
       <c r="J38" t="n">
-        <v>22.9096</v>
+        <v>21.6804</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3318</v>
+        <v>0.3369</v>
       </c>
       <c r="J39" t="n">
-        <v>9.2904</v>
+        <v>9.433199999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.03</v>
       </c>
       <c r="I40" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1052</v>
       </c>
       <c r="J40" t="n">
-        <v>2.408</v>
+        <v>2.9456</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.95</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2489</v>
+        <v>-0.2362</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.9692</v>
+        <v>-6.6136</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.01</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0566</v>
+        <v>0.0569</v>
       </c>
       <c r="J42" t="n">
-        <v>1.0754</v>
+        <v>1.0811</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1057</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.7537</v>
+        <v>-2.0083</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1358</v>
+        <v>-0.1509</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.5802</v>
+        <v>-2.8671</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.88</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1464</v>
+        <v>-0.1618</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.7816</v>
+        <v>-3.0742</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1777</v>
+        <v>-0.1935</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.3763</v>
+        <v>-3.6765</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.92</v>
       </c>
       <c r="I47" t="n">
-        <v>1.6373</v>
+        <v>1.7712</v>
       </c>
       <c r="J47" t="n">
-        <v>31.1087</v>
+        <v>33.6528</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.64</v>
       </c>
       <c r="I48" t="n">
-        <v>1.3012</v>
+        <v>1.3739</v>
       </c>
       <c r="J48" t="n">
-        <v>24.7228</v>
+        <v>26.1041</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.26</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6898</v>
+        <v>0.6636</v>
       </c>
       <c r="J49" t="n">
-        <v>13.1062</v>
+        <v>12.6084</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1691</v>
+        <v>0.1892</v>
       </c>
       <c r="J50" t="n">
-        <v>3.2129</v>
+        <v>3.5948</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.43</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.5547</v>
+        <v>-1.3841</v>
       </c>
       <c r="J51" t="n">
-        <v>-29.5393</v>
+        <v>-26.2979</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1962</v>
+        <v>0.1894</v>
       </c>
       <c r="J52" t="n">
-        <v>3.5316</v>
+        <v>3.4092</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0272</v>
+        <v>-0.0406</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.4896</v>
+        <v>-0.7308</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.148</v>
+        <v>-0.1658</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.664</v>
+        <v>-2.9844</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.285</v>
+        <v>-0.3021</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.13</v>
+        <v>-5.4378</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.49</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5094</v>
+        <v>-0.5164</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.1692</v>
+        <v>-9.295199999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.87</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2594</v>
+        <v>1.3821</v>
       </c>
       <c r="J57" t="n">
-        <v>22.6692</v>
+        <v>24.8778</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.82</v>
       </c>
       <c r="I58" t="n">
-        <v>1.2022</v>
+        <v>1.3219</v>
       </c>
       <c r="J58" t="n">
-        <v>21.6396</v>
+        <v>23.7942</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.67</v>
       </c>
       <c r="I59" t="n">
-        <v>1.0283</v>
+        <v>1.1376</v>
       </c>
       <c r="J59" t="n">
-        <v>18.5094</v>
+        <v>20.4768</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3339</v>
+        <v>-0.3038</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.0102</v>
+        <v>-5.4684</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6186</v>
+        <v>-0.5657</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.1348</v>
+        <v>-10.1826</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>0.84</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1669</v>
+        <v>-0.1877</v>
       </c>
       <c r="J62" t="n">
-        <v>-3.0042</v>
+        <v>-3.3786</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.8</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2086</v>
+        <v>-0.229</v>
       </c>
       <c r="J63" t="n">
-        <v>-3.7548</v>
+        <v>-4.122</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.76</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2477</v>
+        <v>-0.2675</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.4586</v>
+        <v>-4.815</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.74</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2658</v>
+        <v>-0.2854</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.7844</v>
+        <v>-5.1372</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.58</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.415</v>
+        <v>-0.4291</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.47</v>
+        <v>-7.7238</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.87</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2724</v>
+        <v>1.3936</v>
       </c>
       <c r="J67" t="n">
-        <v>22.9032</v>
+        <v>25.0848</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.72</v>
       </c>
       <c r="I68" t="n">
-        <v>1.0975</v>
+        <v>1.2092</v>
       </c>
       <c r="J68" t="n">
-        <v>19.755</v>
+        <v>21.7656</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.18</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4175</v>
+        <v>0.4665</v>
       </c>
       <c r="J69" t="n">
-        <v>7.515</v>
+        <v>8.397</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.13</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3392</v>
+        <v>0.3584</v>
       </c>
       <c r="J70" t="n">
-        <v>6.1056</v>
+        <v>6.4512</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2225</v>
+        <v>-0.2</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.005</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.39</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7187</v>
+        <v>0.7973</v>
       </c>
       <c r="J72" t="n">
-        <v>14.374</v>
+        <v>15.946</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.32</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6963</v>
       </c>
       <c r="J73" t="n">
-        <v>12.53</v>
+        <v>13.926</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.27</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5596</v>
+        <v>0.6221</v>
       </c>
       <c r="J74" t="n">
-        <v>11.192</v>
+        <v>12.442</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3597</v>
+        <v>0.3808</v>
       </c>
       <c r="J75" t="n">
-        <v>7.194</v>
+        <v>7.616</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.05</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1445</v>
+        <v>0.164</v>
       </c>
       <c r="J76" t="n">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.39</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6615</v>
+        <v>0.7239</v>
       </c>
       <c r="J77" t="n">
-        <v>13.23</v>
+        <v>14.478</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2065</v>
+        <v>0.197</v>
       </c>
       <c r="J78" t="n">
-        <v>4.13</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.65</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3578</v>
+        <v>-0.3731</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.156</v>
+        <v>-7.462</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.55</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4512</v>
+        <v>-0.462</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.023999999999999</v>
+        <v>-9.24</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6252</v>
+        <v>-0.6249</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.504</v>
+        <v>-12.498</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.56</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9419</v>
+        <v>1.0368</v>
       </c>
       <c r="J82" t="n">
-        <v>19.7799</v>
+        <v>21.7728</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.56</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9419</v>
+        <v>1.0368</v>
       </c>
       <c r="J83" t="n">
-        <v>19.7799</v>
+        <v>21.7728</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.12</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3465</v>
+        <v>0.3599</v>
       </c>
       <c r="J84" t="n">
-        <v>7.2765</v>
+        <v>7.5579</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0043</v>
+        <v>0.0249</v>
       </c>
       <c r="J85" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.5229</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7027</v>
+        <v>-0.6495</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.7567</v>
+        <v>-13.6395</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.31</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5476</v>
+        <v>0.6016</v>
       </c>
       <c r="J87" t="n">
-        <v>11.4996</v>
+        <v>12.6336</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>0.85</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1731</v>
+        <v>-0.19</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.6351</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1932</v>
+        <v>-0.2103</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.0572</v>
+        <v>-4.4163</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2033</v>
+        <v>-0.2203</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.2693</v>
+        <v>-4.6263</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4696</v>
+        <v>-0.4779</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.861599999999999</v>
+        <v>-10.0359</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>0.91</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1109</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.6434</v>
+        <v>-1.9962</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.83</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1805</v>
+        <v>-0.2006</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.249</v>
+        <v>-3.6108</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.75</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2582</v>
+        <v>-0.2775</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.6476</v>
+        <v>-4.995</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.68</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3237</v>
+        <v>-0.3413</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.8266</v>
+        <v>-6.1434</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.63</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3707</v>
+        <v>-0.3865</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.6726</v>
+        <v>-6.957</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9376</v>
+        <v>1.0352</v>
       </c>
       <c r="J97" t="n">
-        <v>16.8768</v>
+        <v>18.6336</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6593</v>
+        <v>0.734</v>
       </c>
       <c r="J98" t="n">
-        <v>11.8674</v>
+        <v>13.212</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.29</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5813</v>
+        <v>0.6476</v>
       </c>
       <c r="J99" t="n">
-        <v>10.4634</v>
+        <v>11.6568</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4299</v>
+        <v>0.4774</v>
       </c>
       <c r="J100" t="n">
-        <v>7.7382</v>
+        <v>8.5932</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.0677</v>
+        <v>-0.0469</v>
       </c>
       <c r="J101" t="n">
-        <v>-1.2186</v>
+        <v>-0.8442</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3568</v>
+        <v>0.3704</v>
       </c>
       <c r="J102" t="n">
-        <v>12.1312</v>
+        <v>12.5936</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1455</v>
+        <v>0.1523</v>
       </c>
       <c r="J103" t="n">
-        <v>4.947</v>
+        <v>5.1782</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0039</v>
+        <v>0.0027</v>
       </c>
       <c r="J104" t="n">
-        <v>0.1326</v>
+        <v>0.09180000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1421</v>
+        <v>-0.1558</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.8314</v>
+        <v>-5.2972</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.76</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2753</v>
+        <v>-0.2888</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.360200000000001</v>
+        <v>-9.8192</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.44</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7864</v>
+        <v>0.8702</v>
       </c>
       <c r="J107" t="n">
-        <v>26.7376</v>
+        <v>29.5868</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.44</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7864</v>
+        <v>0.8702</v>
       </c>
       <c r="J108" t="n">
-        <v>26.7376</v>
+        <v>29.5868</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.22</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4933</v>
+        <v>0.5474</v>
       </c>
       <c r="J109" t="n">
-        <v>16.7722</v>
+        <v>18.6116</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.04</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1148</v>
+        <v>0.1347</v>
       </c>
       <c r="J110" t="n">
-        <v>3.9032</v>
+        <v>4.5798</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2549</v>
+        <v>-0.2404</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.666600000000001</v>
+        <v>-8.1736</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6792</v>
+        <v>0.7483</v>
       </c>
       <c r="J112" t="n">
-        <v>15.6216</v>
+        <v>17.2109</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.26</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6252</v>
       </c>
       <c r="J113" t="n">
-        <v>13.041</v>
+        <v>14.3796</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3419</v>
+        <v>0.3488</v>
       </c>
       <c r="J114" t="n">
-        <v>7.8637</v>
+        <v>8.022399999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.01</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0308</v>
+        <v>0.0433</v>
       </c>
       <c r="J115" t="n">
-        <v>0.7084</v>
+        <v>0.9959</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.8</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6508</v>
+        <v>-0.6083</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.9684</v>
+        <v>-13.9909</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.18</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3874</v>
+        <v>0.4153</v>
       </c>
       <c r="J117" t="n">
-        <v>8.9102</v>
+        <v>9.5519</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.16</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3647</v>
+        <v>0.3801</v>
       </c>
       <c r="J118" t="n">
-        <v>8.3881</v>
+        <v>8.7423</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0448</v>
+        <v>-0.0542</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.0304</v>
+        <v>-1.2466</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2211</v>
+        <v>-0.2363</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.0853</v>
+        <v>-5.4349</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4678</v>
+        <v>-0.4751</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.7594</v>
+        <v>-10.9273</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.16</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2832</v>
+        <v>0.2887</v>
       </c>
       <c r="J122" t="n">
-        <v>6.2304</v>
+        <v>6.3514</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2387</v>
+        <v>0.2457</v>
       </c>
       <c r="J123" t="n">
-        <v>5.2514</v>
+        <v>5.4054</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.99</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0194</v>
+        <v>-0.0244</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.4268</v>
+        <v>-0.5368000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.93</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.098</v>
+        <v>-0.1099</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.156</v>
+        <v>-2.4178</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3434</v>
+        <v>-0.3551</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.5548</v>
+        <v>-7.8122</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.49</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5028</v>
+        <v>0.5734</v>
       </c>
       <c r="J127" t="n">
-        <v>11.0616</v>
+        <v>12.6148</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.2</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2847</v>
+        <v>0.3013</v>
       </c>
       <c r="J128" t="n">
-        <v>6.2634</v>
+        <v>6.6286</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.19</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2725</v>
+        <v>0.2893</v>
       </c>
       <c r="J129" t="n">
-        <v>5.995</v>
+        <v>6.3646</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0284</v>
+        <v>0.0406</v>
       </c>
       <c r="J130" t="n">
-        <v>0.6248</v>
+        <v>0.8932</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.92</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.129</v>
+        <v>-0.1371</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.838</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>2.22</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6425</v>
+        <v>1.7825</v>
       </c>
       <c r="J132" t="n">
-        <v>26.28</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.5</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8236</v>
+        <v>0.9184</v>
       </c>
       <c r="J133" t="n">
-        <v>13.1776</v>
+        <v>14.6944</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.48</v>
       </c>
       <c r="I134" t="n">
-        <v>0.8</v>
+        <v>0.8927</v>
       </c>
       <c r="J134" t="n">
-        <v>12.8</v>
+        <v>14.2832</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3453</v>
+        <v>0.3703</v>
       </c>
       <c r="J135" t="n">
-        <v>5.5248</v>
+        <v>5.9248</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3077</v>
+        <v>-0.2776</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.9232</v>
+        <v>-4.4416</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.26</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5258</v>
+        <v>0.5703</v>
       </c>
       <c r="J137" t="n">
-        <v>8.412800000000001</v>
+        <v>9.1248</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1416</v>
+        <v>-0.1608</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.2656</v>
+        <v>-2.5728</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.66</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3458</v>
+        <v>-0.362</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.5328</v>
+        <v>-5.792</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.62</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3834</v>
+        <v>-0.398</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.1344</v>
+        <v>-6.368</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.495</v>
+        <v>-0.5037</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.92</v>
+        <v>-8.059200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7912/event_7912_evp_summary.xlsx
+++ b/database/event/7912/event_7912_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.1157</v>
+        <v>8.2722</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3147</v>
+        <v>2.3593</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0702</v>
+        <v>3.0812</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1157</v>
+        <v>8.2722</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.1157</v>
+        <v>8.0801</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3795</v>
+        <v>6.3515</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>189</v>
       </c>
       <c r="M2" t="n">
-        <v>6.3795</v>
+        <v>6.3515</v>
       </c>
       <c r="N2" t="n">
         <v>189</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.665</v>
+        <v>7.71</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1862</v>
+        <v>2.199</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8651</v>
+        <v>2.8301</v>
       </c>
       <c r="E3" t="n">
-        <v>7.665</v>
+        <v>7.71</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.665</v>
+        <v>7.6659</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6.0252</v>
+        <v>6.0259</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0252</v>
+        <v>6.0259</v>
       </c>
       <c r="N3" t="n">
         <v>189</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9646</v>
+        <v>5.3657</v>
       </c>
       <c r="C4" t="n">
-        <v>1.416</v>
+        <v>1.5304</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6358</v>
+        <v>1.7829</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9646</v>
+        <v>5.3657</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9646</v>
+        <v>4.9652</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9025</v>
+        <v>3.903</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>142</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9025</v>
+        <v>3.903</v>
       </c>
       <c r="N4" t="n">
         <v>142</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6574</v>
+        <v>5.0345</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3284</v>
+        <v>1.4359</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4959</v>
+        <v>1.635</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6574</v>
+        <v>5.0345</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6574</v>
+        <v>4.6421</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.661</v>
+        <v>3.649</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>102</v>
       </c>
       <c r="M5" t="n">
-        <v>3.661</v>
+        <v>3.649</v>
       </c>
       <c r="N5" t="n">
         <v>102</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0965</v>
+        <v>4.0997</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1684</v>
+        <v>1.1693</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2406</v>
+        <v>1.2174</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0965</v>
+        <v>4.0997</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0965</v>
+        <v>4.0968</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2201</v>
+        <v>3.2204</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>189</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2201</v>
+        <v>3.2204</v>
       </c>
       <c r="N6" t="n">
         <v>189</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8426</v>
+        <v>2.8739</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8107</v>
+        <v>0.8197</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6698</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8426</v>
+        <v>2.8739</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8426</v>
+        <v>2.8434</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2345</v>
+        <v>2.2351</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>142</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2345</v>
+        <v>2.2351</v>
       </c>
       <c r="N7" t="n">
         <v>142</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.49</v>
+        <v>2.4068</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6865</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5093</v>
+        <v>0.4612</v>
       </c>
       <c r="E8" t="n">
-        <v>2.49</v>
+        <v>2.4068</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.49</v>
+        <v>2.4909</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9573</v>
+        <v>1.958</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>189</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9573</v>
+        <v>1.958</v>
       </c>
       <c r="N8" t="n">
         <v>189</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5893</v>
+        <v>1.4925</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4533</v>
+        <v>0.4257</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0993</v>
+        <v>0.0528</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5893</v>
+        <v>1.4925</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5893</v>
+        <v>1.5901</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2493</v>
+        <v>1.2499</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>189</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2493</v>
+        <v>1.2499</v>
       </c>
       <c r="N9" t="n">
         <v>189</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6974</v>
+        <v>0.7938</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1989</v>
+        <v>0.2264</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3067</v>
+        <v>-0.2592</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6974</v>
+        <v>0.7938</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6974</v>
+        <v>0.6975</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5482</v>
+        <v>0.5483</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>102</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5482</v>
+        <v>0.5483</v>
       </c>
       <c r="N10" t="n">
         <v>102</v>
@@ -906,26 +906,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4819</v>
+        <v>0.6703</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1374</v>
+        <v>0.1912</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4048</v>
+        <v>-0.3144</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4819</v>
+        <v>0.6703</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4819</v>
+        <v>0.4053</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,44 +934,44 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3788</v>
+        <v>0.3186</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3788</v>
+        <v>0.3186</v>
       </c>
       <c r="N11" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4765</v>
+        <v>0.3226</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1359</v>
+        <v>0.092</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4073</v>
+        <v>-0.4697</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4765</v>
+        <v>0.3226</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4765</v>
+        <v>0.2786</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,19 +980,19 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3746</v>
+        <v>0.219</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3746</v>
+        <v>0.219</v>
       </c>
       <c r="N12" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4608</v>
+        <v>0.3163</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1314</v>
+        <v>0.0902</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4144</v>
+        <v>-0.4725</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4608</v>
+        <v>0.3163</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4608</v>
+        <v>0.4447</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3622</v>
+        <v>0.3496</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>102</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3622</v>
+        <v>0.3496</v>
       </c>
       <c r="N13" t="n">
         <v>102</v>
@@ -1044,26 +1044,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4053</v>
+        <v>0.316</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1156</v>
+        <v>0.0901</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4397</v>
+        <v>-0.4727</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4053</v>
+        <v>0.316</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4053</v>
+        <v>0.4765</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3186</v>
+        <v>0.3746</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>61</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3186</v>
+        <v>0.3746</v>
       </c>
       <c r="N14" t="n">
         <v>61</v>
@@ -1090,26 +1090,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3582</v>
+        <v>0.252</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1022</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4611</v>
+        <v>-0.5013</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3582</v>
+        <v>0.252</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3582</v>
+        <v>0.1046</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2816</v>
+        <v>0.0822</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2816</v>
+        <v>0.0822</v>
       </c>
       <c r="N15" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2969</v>
+        <v>0.2025</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0847</v>
+        <v>0.0578</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.489</v>
+        <v>-0.5234</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2969</v>
+        <v>0.2025</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2969</v>
+        <v>0.4622</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2334</v>
+        <v>0.3633</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>142</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2334</v>
+        <v>0.3633</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1182,26 +1182,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HexT</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2</v>
+        <v>0.1345</v>
       </c>
       <c r="C17" t="n">
-        <v>0.057</v>
+        <v>0.0384</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5332</v>
+        <v>-0.5537</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>0.1345</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2</v>
+        <v>0.037</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1572</v>
+        <v>0.0291</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1572</v>
+        <v>0.0291</v>
       </c>
       <c r="N17" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>HexT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1046</v>
+        <v>0.1319</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0298</v>
+        <v>0.0376</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5766</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1046</v>
+        <v>0.1319</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1046</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0822</v>
+        <v>0.1572</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0822</v>
+        <v>0.1572</v>
       </c>
       <c r="N18" t="n">
         <v>61</v>
@@ -1274,26 +1274,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1052</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0209</v>
+        <v>0.03</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5908</v>
+        <v>-0.5668</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1052</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.3589</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,44 +1302,44 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0577</v>
+        <v>0.2821</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0577</v>
+        <v>0.2821</v>
       </c>
       <c r="N19" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0527</v>
+        <v>-0.0523</v>
       </c>
       <c r="C20" t="n">
-        <v>0.015</v>
+        <v>-0.0149</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6002</v>
+        <v>-0.6372</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0527</v>
+        <v>-0.0523</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0527</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,44 +1348,44 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0414</v>
+        <v>0.0684</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0414</v>
+        <v>0.0684</v>
       </c>
       <c r="N20" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.037</v>
+        <v>-0.067</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0106</v>
+        <v>-0.0191</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.6437</v>
       </c>
       <c r="E21" t="n">
-        <v>0.037</v>
+        <v>-0.067</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.037</v>
+        <v>0.0527</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0291</v>
+        <v>0.0414</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>52</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0291</v>
+        <v>0.0414</v>
       </c>
       <c r="N21" t="n">
         <v>52</v>
@@ -1412,26 +1412,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3049</v>
+        <v>-0.1723</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0491</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.763</v>
+        <v>-0.6908</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3049</v>
+        <v>-0.1723</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3049</v>
+        <v>-0.4883</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2397</v>
+        <v>-0.3838</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2397</v>
+        <v>-0.3838</v>
       </c>
       <c r="N22" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.343</v>
+        <v>-0.195</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0978</v>
+        <v>-0.0556</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7803</v>
+        <v>-0.7009</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.343</v>
+        <v>-0.195</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.343</v>
+        <v>-0.2759</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2696</v>
+        <v>-0.2169</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>36</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2696</v>
+        <v>-0.2169</v>
       </c>
       <c r="N23" t="n">
         <v>36</v>
@@ -1504,26 +1504,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.4883</v>
+        <v>-0.4585</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1393</v>
+        <v>-0.1308</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8465</v>
+        <v>-0.8186</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4883</v>
+        <v>-0.4585</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4883</v>
+        <v>-0.5743</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3838</v>
+        <v>-0.4514</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3838</v>
+        <v>-0.4514</v>
       </c>
       <c r="N24" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5512</v>
+        <v>-0.5784</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1572</v>
+        <v>-0.165</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8751</v>
+        <v>-0.8722</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5512</v>
+        <v>-0.5784</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5512</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4333</v>
+        <v>-0.4901</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4333</v>
+        <v>-0.4901</v>
       </c>
       <c r="N25" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.574</v>
+        <v>-0.631</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1637</v>
+        <v>-0.18</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8855</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.574</v>
+        <v>-0.631</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.574</v>
+        <v>-0.5512</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4512</v>
+        <v>-0.4333</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4512</v>
+        <v>-0.4333</v>
       </c>
       <c r="N26" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6226</v>
+        <v>-0.6889</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1776</v>
+        <v>-0.1965</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9076</v>
+        <v>-0.9215</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6226</v>
+        <v>-0.6889</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6226</v>
+        <v>-0.3434</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4894</v>
+        <v>-0.2699</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4894</v>
+        <v>-0.2699</v>
       </c>
       <c r="N27" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6231</v>
+        <v>-0.9052</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1777</v>
+        <v>-0.2582</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9079</v>
+        <v>-1.0182</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6231</v>
+        <v>-0.9052</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6231</v>
+        <v>-0.6226</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4898</v>
+        <v>-0.4894</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4898</v>
+        <v>-0.4894</v>
       </c>
       <c r="N28" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.8772</v>
+        <v>-0.9658</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2502</v>
+        <v>-0.2755</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0235</v>
+        <v>-1.0452</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.8772</v>
+        <v>-0.9658</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.8772</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6895</v>
+        <v>-0.7841</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6895</v>
+        <v>-0.7841</v>
       </c>
       <c r="N29" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.9972</v>
+        <v>-0.9886</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2844</v>
+        <v>-0.282</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0781</v>
+        <v>-1.0554</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.9972</v>
+        <v>-0.9886</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.9972</v>
+        <v>-0.8772</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,19 +1808,19 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7839</v>
+        <v>-0.6895</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7839</v>
+        <v>-0.6895</v>
       </c>
       <c r="N30" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0486</v>
+        <v>-1.2195</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2991</v>
+        <v>-0.3478</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.1015</v>
+        <v>-1.1585</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0486</v>
+        <v>-1.2195</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.0486</v>
+        <v>-1.0479</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8243</v>
+        <v>-0.8237</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>102</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8243</v>
+        <v>-0.8237</v>
       </c>
       <c r="N31" t="n">
         <v>102</v>
@@ -3166,13 +3166,13 @@
         <v>28</v>
       </c>
       <c r="H32" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5933</v>
+        <v>0.5775</v>
       </c>
       <c r="J32" t="n">
-        <v>16.6124</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0569</v>
+        <v>0.0573</v>
       </c>
       <c r="J33" t="n">
-        <v>1.5932</v>
+        <v>1.6044</v>
       </c>
     </row>
     <row r="34">
@@ -3249,16 +3249,16 @@
         <v>0.83</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2141</v>
+        <v>-0.2139</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.9948</v>
+        <v>-5.9892</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3289,16 +3289,16 @@
         <v>0.72</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3208</v>
+        <v>-0.3206</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.9824</v>
+        <v>-8.976800000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3329,10 +3329,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3208</v>
+        <v>-0.3206</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.9824</v>
+        <v>-8.976800000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3966,13 +3966,13 @@
         <v>18</v>
       </c>
       <c r="H52" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1894</v>
+        <v>0.2122</v>
       </c>
       <c r="J52" t="n">
-        <v>3.4092</v>
+        <v>3.8196</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0406</v>
+        <v>-0.0409</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.7308</v>
+        <v>-0.7362</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1658</v>
+        <v>-0.166</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.9844</v>
+        <v>-2.988</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3021</v>
+        <v>-0.3024</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.4378</v>
+        <v>-5.4432</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.49</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5164</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.295199999999999</v>
+        <v>-9.2988</v>
       </c>
     </row>
     <row r="57">
@@ -4769,10 +4769,10 @@
         <v>1.39</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7973</v>
+        <v>0.7976</v>
       </c>
       <c r="J72" t="n">
-        <v>15.946</v>
+        <v>15.952</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.32</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6963</v>
+        <v>0.6966</v>
       </c>
       <c r="J73" t="n">
-        <v>13.926</v>
+        <v>13.932</v>
       </c>
     </row>
     <row r="74">
@@ -4846,13 +4846,13 @@
         <v>20</v>
       </c>
       <c r="H74" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6221</v>
+        <v>0.6073</v>
       </c>
       <c r="J74" t="n">
-        <v>12.442</v>
+        <v>12.146</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3808</v>
+        <v>0.3811</v>
       </c>
       <c r="J75" t="n">
-        <v>7.616</v>
+        <v>7.622</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.05</v>
       </c>
       <c r="I76" t="n">
-        <v>0.164</v>
+        <v>0.1644</v>
       </c>
       <c r="J76" t="n">
-        <v>3.28</v>
+        <v>3.288</v>
       </c>
     </row>
     <row r="77">
@@ -5369,10 +5369,10 @@
         <v>1.31</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6016</v>
+        <v>0.6009</v>
       </c>
       <c r="J87" t="n">
-        <v>12.6336</v>
+        <v>12.6189</v>
       </c>
     </row>
     <row r="88">
@@ -5406,13 +5406,13 @@
         <v>21</v>
       </c>
       <c r="H88" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.99</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2103</v>
+        <v>-0.2105</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.4163</v>
+        <v>-4.4205</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2203</v>
+        <v>-0.2205</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.6263</v>
+        <v>-4.6305</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4779</v>
+        <v>-0.4781</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.0359</v>
+        <v>-10.0401</v>
       </c>
     </row>
     <row r="92">
@@ -5769,10 +5769,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0352</v>
+        <v>1.0356</v>
       </c>
       <c r="J97" t="n">
-        <v>18.6336</v>
+        <v>18.6408</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.734</v>
+        <v>0.7342</v>
       </c>
       <c r="J98" t="n">
-        <v>13.212</v>
+        <v>13.2156</v>
       </c>
     </row>
     <row r="99">
@@ -5846,13 +5846,13 @@
         <v>18</v>
       </c>
       <c r="H99" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6476</v>
+        <v>0.6333</v>
       </c>
       <c r="J99" t="n">
-        <v>11.6568</v>
+        <v>11.3994</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4774</v>
+        <v>0.4777</v>
       </c>
       <c r="J100" t="n">
-        <v>8.5932</v>
+        <v>8.598599999999999</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.0469</v>
+        <v>-0.0466</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.8442</v>
+        <v>-0.8388</v>
       </c>
     </row>
     <row r="102">
@@ -6169,10 +6169,10 @@
         <v>1.44</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8702</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>29.5868</v>
+        <v>29.597</v>
       </c>
     </row>
     <row r="108">
@@ -6206,13 +6206,13 @@
         <v>34</v>
       </c>
       <c r="H108" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8702</v>
+        <v>0.8565</v>
       </c>
       <c r="J108" t="n">
-        <v>29.5868</v>
+        <v>29.121</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.22</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5474</v>
+        <v>0.5475</v>
       </c>
       <c r="J109" t="n">
-        <v>18.6116</v>
+        <v>18.615</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.04</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1347</v>
+        <v>0.1351</v>
       </c>
       <c r="J110" t="n">
-        <v>4.5798</v>
+        <v>4.5934</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2404</v>
+        <v>-0.2401</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.1736</v>
+        <v>-8.163399999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7483</v>
+        <v>0.7488</v>
       </c>
       <c r="J112" t="n">
-        <v>17.2109</v>
+        <v>17.2224</v>
       </c>
     </row>
     <row r="113">
@@ -6406,13 +6406,13 @@
         <v>23</v>
       </c>
       <c r="H113" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6252</v>
+        <v>0.6098</v>
       </c>
       <c r="J113" t="n">
-        <v>14.3796</v>
+        <v>14.0254</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3488</v>
+        <v>0.349</v>
       </c>
       <c r="J114" t="n">
-        <v>8.022399999999999</v>
+        <v>8.026999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.01</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0433</v>
+        <v>0.0436</v>
       </c>
       <c r="J115" t="n">
-        <v>0.9959</v>
+        <v>1.0028</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.8</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6083</v>
+        <v>-0.6079</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.9909</v>
+        <v>-13.9817</v>
       </c>
     </row>
     <row r="117">
@@ -7169,10 +7169,10 @@
         <v>2.22</v>
       </c>
       <c r="I132" t="n">
-        <v>1.7825</v>
+        <v>1.7831</v>
       </c>
       <c r="J132" t="n">
-        <v>28.52</v>
+        <v>28.5296</v>
       </c>
     </row>
     <row r="133">
@@ -7206,13 +7206,13 @@
         <v>16</v>
       </c>
       <c r="H133" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9184</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="J133" t="n">
-        <v>14.6944</v>
+        <v>14.4912</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.48</v>
       </c>
       <c r="I134" t="n">
-        <v>0.8927</v>
+        <v>0.8928</v>
       </c>
       <c r="J134" t="n">
-        <v>14.2832</v>
+        <v>14.2848</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3703</v>
+        <v>0.3706</v>
       </c>
       <c r="J135" t="n">
-        <v>5.9248</v>
+        <v>5.9296</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2776</v>
+        <v>-0.2773</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.4416</v>
+        <v>-4.4368</v>
       </c>
     </row>
     <row r="137">

--- a/database/event/7912/event_7912_evp_summary.xlsx
+++ b/database/event/7912/event_7912_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.2722</v>
+        <v>8.287699999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3593</v>
+        <v>2.3638</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0812</v>
+        <v>3.1697</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2722</v>
+        <v>8.287699999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.0801</v>
+        <v>8.095599999999999</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3515</v>
+        <v>6.4005</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>189</v>
       </c>
       <c r="M2" t="n">
-        <v>6.3515</v>
+        <v>6.4005</v>
       </c>
       <c r="N2" t="n">
         <v>189</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.71</v>
+        <v>7.6518</v>
       </c>
       <c r="C3" t="n">
-        <v>2.199</v>
+        <v>2.1824</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8301</v>
+        <v>2.88</v>
       </c>
       <c r="E3" t="n">
-        <v>7.71</v>
+        <v>7.6518</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.6659</v>
+        <v>7.6077</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6.0259</v>
+        <v>6.0148</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0259</v>
+        <v>6.0148</v>
       </c>
       <c r="N3" t="n">
         <v>189</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3657</v>
+        <v>5.1975</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5304</v>
+        <v>1.4824</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7829</v>
+        <v>1.7619</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3657</v>
+        <v>5.1975</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9652</v>
+        <v>4.797</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.903</v>
+        <v>3.7926</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>142</v>
       </c>
       <c r="M4" t="n">
-        <v>3.903</v>
+        <v>3.7926</v>
       </c>
       <c r="N4" t="n">
         <v>142</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0345</v>
+        <v>5.0033</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4359</v>
+        <v>1.427</v>
       </c>
       <c r="D5" t="n">
-        <v>1.635</v>
+        <v>1.6735</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0345</v>
+        <v>5.0033</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6421</v>
+        <v>4.6109</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.649</v>
+        <v>3.6454</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>102</v>
       </c>
       <c r="M5" t="n">
-        <v>3.649</v>
+        <v>3.6454</v>
       </c>
       <c r="N5" t="n">
         <v>102</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0997</v>
+        <v>3.9952</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1693</v>
+        <v>1.1395</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2174</v>
+        <v>1.2142</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0997</v>
+        <v>3.9952</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0968</v>
+        <v>3.9923</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2204</v>
+        <v>3.1564</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>189</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2204</v>
+        <v>3.1564</v>
       </c>
       <c r="N6" t="n">
         <v>189</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8739</v>
+        <v>2.6404</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8197</v>
+        <v>0.7531</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.597</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8739</v>
+        <v>2.6404</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8434</v>
+        <v>2.6099</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2351</v>
+        <v>2.0634</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>142</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2351</v>
+        <v>2.0634</v>
       </c>
       <c r="N7" t="n">
         <v>142</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4068</v>
+        <v>2.3775</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6865</v>
+        <v>0.6781</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4612</v>
+        <v>0.4773</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4068</v>
+        <v>2.3775</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4909</v>
+        <v>2.4616</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.958</v>
+        <v>1.9461</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>189</v>
       </c>
       <c r="M8" t="n">
-        <v>1.958</v>
+        <v>1.9461</v>
       </c>
       <c r="N8" t="n">
         <v>189</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.4925</v>
+        <v>1.5087</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4257</v>
+        <v>0.4303</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0528</v>
+        <v>0.0815</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4925</v>
+        <v>1.5087</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5901</v>
+        <v>1.6063</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2499</v>
+        <v>1.27</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>189</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2499</v>
+        <v>1.27</v>
       </c>
       <c r="N9" t="n">
         <v>189</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7938</v>
+        <v>0.794</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2264</v>
+        <v>0.2265</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2592</v>
+        <v>-0.2441</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7938</v>
+        <v>0.794</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6975</v>
+        <v>0.6977</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5483</v>
+        <v>0.5516</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>102</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5483</v>
+        <v>0.5516</v>
       </c>
       <c r="N10" t="n">
         <v>102</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6703</v>
+        <v>0.543</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1912</v>
+        <v>0.1549</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3144</v>
+        <v>-0.3584</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6703</v>
+        <v>0.543</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4053</v>
+        <v>0.278</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3186</v>
+        <v>0.2198</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>61</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3186</v>
+        <v>0.2198</v>
       </c>
       <c r="N11" t="n">
         <v>61</v>
@@ -952,26 +952,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3226</v>
+        <v>0.3015</v>
       </c>
       <c r="C12" t="n">
-        <v>0.092</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4697</v>
+        <v>-0.4684</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3226</v>
+        <v>0.3015</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2786</v>
+        <v>0.462</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,19 +980,19 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.219</v>
+        <v>0.3653</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>0.219</v>
+        <v>0.3653</v>
       </c>
       <c r="N12" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3163</v>
+        <v>0.2698</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0902</v>
+        <v>0.077</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4725</v>
+        <v>-0.4829</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3163</v>
+        <v>0.2698</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4447</v>
+        <v>0.3982</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3496</v>
+        <v>0.3148</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>102</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3496</v>
+        <v>0.3148</v>
       </c>
       <c r="N13" t="n">
         <v>102</v>
@@ -1044,26 +1044,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.316</v>
+        <v>0.2255</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0901</v>
+        <v>0.0643</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4727</v>
+        <v>-0.5031</v>
       </c>
       <c r="E14" t="n">
-        <v>0.316</v>
+        <v>0.2255</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4765</v>
+        <v>0.0781</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3746</v>
+        <v>0.0618</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>61</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3746</v>
+        <v>0.0618</v>
       </c>
       <c r="N14" t="n">
         <v>61</v>
@@ -1090,26 +1090,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.252</v>
+        <v>0.1724</v>
       </c>
       <c r="C15" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0492</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5013</v>
+        <v>-0.5273</v>
       </c>
       <c r="E15" t="n">
-        <v>0.252</v>
+        <v>0.1724</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1046</v>
+        <v>0.1284</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0822</v>
+        <v>0.1015</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0822</v>
+        <v>0.1015</v>
       </c>
       <c r="N15" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2025</v>
+        <v>0.1231</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0578</v>
+        <v>0.0351</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5234</v>
+        <v>-0.5497</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2025</v>
+        <v>0.1231</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4622</v>
+        <v>0.3768</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3633</v>
+        <v>0.2979</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>142</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3633</v>
+        <v>0.2979</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1182,26 +1182,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>HexT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1345</v>
+        <v>0.116</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0384</v>
+        <v>0.0331</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5537</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1345</v>
+        <v>0.116</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.037</v>
+        <v>0.1841</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0291</v>
+        <v>0.1456</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0291</v>
+        <v>0.1456</v>
       </c>
       <c r="N17" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HexT</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1319</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0376</v>
+        <v>0.0238</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.5677</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1319</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2</v>
+        <v>-0.0139</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,44 +1256,44 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1572</v>
+        <v>-0.011</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1572</v>
+        <v>-0.011</v>
       </c>
       <c r="N18" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1052</v>
+        <v>0.0755</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03</v>
+        <v>0.0215</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5668</v>
+        <v>-0.5714</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1052</v>
+        <v>0.0755</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3589</v>
+        <v>0.3352</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2821</v>
+        <v>0.265</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>142</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2821</v>
+        <v>0.265</v>
       </c>
       <c r="N19" t="n">
         <v>142</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0523</v>
+        <v>-0.0857</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0149</v>
+        <v>-0.0244</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6372</v>
+        <v>-0.6448</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0523</v>
+        <v>-0.0857</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0536</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0684</v>
+        <v>0.0424</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>102</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0684</v>
+        <v>0.0424</v>
       </c>
       <c r="N20" t="n">
         <v>102</v>
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.067</v>
+        <v>-0.0936</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0191</v>
+        <v>-0.0267</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6437</v>
+        <v>-0.6484</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.067</v>
+        <v>-0.0936</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0527</v>
+        <v>0.0261</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0414</v>
+        <v>0.0207</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>52</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0414</v>
+        <v>0.0207</v>
       </c>
       <c r="N21" t="n">
         <v>52</v>
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1723</v>
+        <v>-0.1555</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0491</v>
+        <v>-0.0444</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6908</v>
+        <v>-0.6766</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1723</v>
+        <v>-0.1555</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4883</v>
+        <v>-0.4715</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3838</v>
+        <v>-0.3728</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>52</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3838</v>
+        <v>-0.3728</v>
       </c>
       <c r="N22" t="n">
         <v>52</v>
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.195</v>
+        <v>-0.232</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0556</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7009</v>
+        <v>-0.7115</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.195</v>
+        <v>-0.232</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2759</v>
+        <v>-0.3129</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2169</v>
+        <v>-0.2474</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>36</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2169</v>
+        <v>-0.2474</v>
       </c>
       <c r="N23" t="n">
         <v>36</v>
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.4585</v>
+        <v>-0.4143</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1308</v>
+        <v>-0.1182</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8186</v>
+        <v>-0.7945</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4585</v>
+        <v>-0.4143</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5743</v>
+        <v>-0.5301</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4514</v>
+        <v>-0.4191</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>36</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4514</v>
+        <v>-0.4191</v>
       </c>
       <c r="N24" t="n">
         <v>36</v>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5784</v>
+        <v>-0.5331</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.165</v>
+        <v>-0.152</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8722</v>
+        <v>-0.8486</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5784</v>
+        <v>-0.5331</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.5782</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4901</v>
+        <v>-0.4571</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>36</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4901</v>
+        <v>-0.4571</v>
       </c>
       <c r="N25" t="n">
         <v>36</v>
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.631</v>
+        <v>-0.5824</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.18</v>
+        <v>-0.1661</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.8711</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.631</v>
+        <v>-0.5824</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5512</v>
+        <v>-0.5026</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4333</v>
+        <v>-0.3974</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4333</v>
+        <v>-0.3974</v>
       </c>
       <c r="N26" t="n">
         <v>52</v>
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6889</v>
+        <v>-0.6554</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1965</v>
+        <v>-0.1869</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9215</v>
+        <v>-0.9044</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6889</v>
+        <v>-0.6554</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3434</v>
+        <v>-0.3099</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2699</v>
+        <v>-0.245</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2699</v>
+        <v>-0.245</v>
       </c>
       <c r="N27" t="n">
         <v>36</v>
@@ -1692,22 +1692,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.9052</v>
+        <v>-0.8578</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2582</v>
+        <v>-0.2447</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0182</v>
+        <v>-0.9966</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.9052</v>
+        <v>-0.8578</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6226</v>
+        <v>-0.5752</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4894</v>
+        <v>-0.4548</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>52</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4894</v>
+        <v>-0.4548</v>
       </c>
       <c r="N28" t="n">
         <v>52</v>
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9658</v>
+        <v>-0.9423</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2755</v>
+        <v>-0.2688</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0452</v>
+        <v>-1.0351</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9658</v>
+        <v>-0.9423</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.974</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7841</v>
+        <v>-0.7701</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7841</v>
+        <v>-0.7701</v>
       </c>
       <c r="N29" t="n">
         <v>36</v>
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.9886</v>
+        <v>-1.0457</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.282</v>
+        <v>-0.2982</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0554</v>
+        <v>-1.0822</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.9886</v>
+        <v>-1.0457</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8772</v>
+        <v>-0.9343</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6895</v>
+        <v>-0.7387</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>61</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6895</v>
+        <v>-0.7387</v>
       </c>
       <c r="N30" t="n">
         <v>61</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.2195</v>
+        <v>-1.167</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3478</v>
+        <v>-0.3328</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.1585</v>
+        <v>-1.1374</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.2195</v>
+        <v>-1.167</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.0479</v>
+        <v>-0.9954</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8237</v>
+        <v>-0.787</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>102</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8237</v>
+        <v>-0.787</v>
       </c>
       <c r="N31" t="n">
         <v>102</v>
@@ -1969,10 +1969,10 @@
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1688</v>
+        <v>0.1353</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7008</v>
+        <v>2.1648</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1428</v>
+        <v>0.1128</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2848</v>
+        <v>1.8048</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0041</v>
+        <v>0.0007</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.51</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.498</v>
+        <v>-0.4969</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.968</v>
+        <v>-7.9504</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5238</v>
+        <v>-0.5263</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.380800000000001</v>
+        <v>-8.4208</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1888</v>
+        <v>1.2048</v>
       </c>
       <c r="J7" t="n">
-        <v>19.0208</v>
+        <v>19.2768</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8465</v>
+        <v>0.833</v>
       </c>
       <c r="J8" t="n">
-        <v>13.544</v>
+        <v>13.328</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.34</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.7933</v>
       </c>
       <c r="J9" t="n">
-        <v>12.944</v>
+        <v>12.6928</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.751</v>
+        <v>0.7322</v>
       </c>
       <c r="J10" t="n">
-        <v>12.016</v>
+        <v>11.7152</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>1.29</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7114</v>
+        <v>0.6905</v>
       </c>
       <c r="J11" t="n">
-        <v>11.3824</v>
+        <v>11.048</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>2.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5666</v>
+        <v>1.5404</v>
       </c>
       <c r="J12" t="n">
-        <v>29.7654</v>
+        <v>29.2676</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.42</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5244</v>
+        <v>0.4585</v>
       </c>
       <c r="J13" t="n">
-        <v>9.9636</v>
+        <v>8.711499999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.13</v>
       </c>
       <c r="I14" t="n">
-        <v>0.197</v>
+        <v>0.1578</v>
       </c>
       <c r="J14" t="n">
-        <v>3.743</v>
+        <v>2.9982</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1395</v>
+        <v>-0.1228</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.6505</v>
+        <v>-2.3332</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.76</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3181</v>
+        <v>-0.3054</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.0439</v>
+        <v>-5.8026</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.508</v>
+        <v>0.5272</v>
       </c>
       <c r="J17" t="n">
-        <v>9.651999999999999</v>
+        <v>10.0168</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3739</v>
+        <v>0.3729</v>
       </c>
       <c r="J18" t="n">
-        <v>7.1041</v>
+        <v>7.0851</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1991</v>
+        <v>-0.1806</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.7829</v>
+        <v>-3.4314</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4328</v>
+        <v>-0.4246</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.2232</v>
+        <v>-8.067399999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.35</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6375</v>
+        <v>-0.6595</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.1125</v>
+        <v>-12.5305</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.9</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9076</v>
       </c>
       <c r="J22" t="n">
-        <v>18.5117</v>
+        <v>17.2444</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.56</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6603</v>
+        <v>0.5896</v>
       </c>
       <c r="J23" t="n">
-        <v>12.5457</v>
+        <v>11.2024</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.37</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4738</v>
+        <v>0.4112</v>
       </c>
       <c r="J24" t="n">
-        <v>9.0022</v>
+        <v>7.8128</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.11</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1682</v>
+        <v>0.1325</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1958</v>
+        <v>2.5175</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.98</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0708</v>
+        <v>-0.0598</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.3452</v>
+        <v>-1.1362</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.92</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.107</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.033</v>
+        <v>-1.7632</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.89</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1424</v>
+        <v>-0.1268</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.7056</v>
+        <v>-2.4092</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2255</v>
+        <v>-0.2078</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.2845</v>
+        <v>-3.9482</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.72</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3104</v>
+        <v>-0.2935</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.8976</v>
+        <v>-5.5765</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3104</v>
+        <v>-0.2935</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.8976</v>
+        <v>-5.5765</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5775</v>
+        <v>0.5219</v>
       </c>
       <c r="J32" t="n">
-        <v>16.17</v>
+        <v>14.6132</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0573</v>
+        <v>0.0392</v>
       </c>
       <c r="J33" t="n">
-        <v>1.6044</v>
+        <v>1.0976</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.83</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2139</v>
+        <v>-0.1939</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.9892</v>
+        <v>-5.4292</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.72</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3206</v>
+        <v>-0.3036</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.976800000000001</v>
+        <v>-8.5008</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3206</v>
+        <v>-0.3036</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.976800000000001</v>
+        <v>-8.5008</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.57</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2701</v>
+        <v>1.2948</v>
       </c>
       <c r="J37" t="n">
-        <v>35.5628</v>
+        <v>36.2544</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7743</v>
+        <v>0.7482</v>
       </c>
       <c r="J38" t="n">
-        <v>21.6804</v>
+        <v>20.9496</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3369</v>
+        <v>0.3034</v>
       </c>
       <c r="J39" t="n">
-        <v>9.433199999999999</v>
+        <v>8.495200000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.03</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1052</v>
+        <v>0.0847</v>
       </c>
       <c r="J40" t="n">
-        <v>2.9456</v>
+        <v>2.3716</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.95</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2362</v>
+        <v>-0.1996</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.6136</v>
+        <v>-5.5888</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.01</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0569</v>
+        <v>0.0389</v>
       </c>
       <c r="J42" t="n">
-        <v>1.0811</v>
+        <v>0.7391</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1057</v>
+        <v>-0.0901</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.0083</v>
+        <v>-1.7119</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1509</v>
+        <v>-0.1325</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.8671</v>
+        <v>-2.5175</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.88</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1618</v>
+        <v>-0.1429</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.0742</v>
+        <v>-2.7151</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1935</v>
+        <v>-0.1738</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.6765</v>
+        <v>-3.3022</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.92</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7712</v>
+        <v>1.814</v>
       </c>
       <c r="J47" t="n">
-        <v>33.6528</v>
+        <v>34.466</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.64</v>
       </c>
       <c r="I48" t="n">
-        <v>1.3739</v>
+        <v>1.4085</v>
       </c>
       <c r="J48" t="n">
-        <v>26.1041</v>
+        <v>26.7615</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.26</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6636</v>
+        <v>0.6357</v>
       </c>
       <c r="J49" t="n">
-        <v>12.6084</v>
+        <v>12.0783</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1892</v>
+        <v>0.1615</v>
       </c>
       <c r="J50" t="n">
-        <v>3.5948</v>
+        <v>3.0685</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.43</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.3841</v>
+        <v>-1.4482</v>
       </c>
       <c r="J51" t="n">
-        <v>-26.2979</v>
+        <v>-27.5158</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.06</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2122</v>
+        <v>0.1727</v>
       </c>
       <c r="J52" t="n">
-        <v>3.8196</v>
+        <v>3.1086</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>0.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0409</v>
+        <v>-0.0317</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.7362</v>
+        <v>-0.5706</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.166</v>
+        <v>-0.1493</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.988</v>
+        <v>-2.6874</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.73</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3024</v>
+        <v>-0.285</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.4432</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.49</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5183</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.2988</v>
+        <v>-9.3294</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.87</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3821</v>
+        <v>1.3902</v>
       </c>
       <c r="J57" t="n">
-        <v>24.8778</v>
+        <v>25.0236</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.82</v>
       </c>
       <c r="I58" t="n">
-        <v>1.3219</v>
+        <v>1.3256</v>
       </c>
       <c r="J58" t="n">
-        <v>23.7942</v>
+        <v>23.8608</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>1.67</v>
       </c>
       <c r="I59" t="n">
-        <v>1.1376</v>
+        <v>1.1316</v>
       </c>
       <c r="J59" t="n">
-        <v>20.4768</v>
+        <v>20.3688</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3038</v>
+        <v>-0.2713</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.4684</v>
+        <v>-4.8834</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5657</v>
+        <v>-0.5355</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.1826</v>
+        <v>-9.638999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>0.84</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1877</v>
+        <v>-0.1721</v>
       </c>
       <c r="J62" t="n">
-        <v>-3.3786</v>
+        <v>-3.0978</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>0.8</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.229</v>
+        <v>-0.2133</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.122</v>
+        <v>-3.8394</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.76</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2675</v>
+        <v>-0.2518</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.815</v>
+        <v>-4.5324</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.74</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2854</v>
+        <v>-0.2698</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.1372</v>
+        <v>-4.8564</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.58</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4291</v>
+        <v>-0.4201</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.7238</v>
+        <v>-7.5618</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.87</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3936</v>
+        <v>1.403</v>
       </c>
       <c r="J67" t="n">
-        <v>25.0848</v>
+        <v>25.254</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.72</v>
       </c>
       <c r="I68" t="n">
-        <v>1.2092</v>
+        <v>1.206</v>
       </c>
       <c r="J68" t="n">
-        <v>21.7656</v>
+        <v>21.708</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.18</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4665</v>
+        <v>0.4465</v>
       </c>
       <c r="J69" t="n">
-        <v>8.397</v>
+        <v>8.037000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.13</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3584</v>
+        <v>0.3264</v>
       </c>
       <c r="J70" t="n">
-        <v>6.4512</v>
+        <v>5.8752</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2</v>
+        <v>-0.172</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.6</v>
+        <v>-3.096</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.39</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7976</v>
+        <v>0.7826</v>
       </c>
       <c r="J72" t="n">
-        <v>15.952</v>
+        <v>15.652</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.32</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6966</v>
+        <v>0.6836</v>
       </c>
       <c r="J73" t="n">
-        <v>13.932</v>
+        <v>13.672</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.26</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6073</v>
+        <v>0.5981</v>
       </c>
       <c r="J74" t="n">
-        <v>12.146</v>
+        <v>11.962</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3811</v>
+        <v>0.3478</v>
       </c>
       <c r="J75" t="n">
-        <v>7.622</v>
+        <v>6.956</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.05</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1644</v>
+        <v>0.1384</v>
       </c>
       <c r="J76" t="n">
-        <v>3.288</v>
+        <v>2.768</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.39</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7239</v>
+        <v>0.7057</v>
       </c>
       <c r="J77" t="n">
-        <v>14.478</v>
+        <v>14.114</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.197</v>
+        <v>0.1608</v>
       </c>
       <c r="J78" t="n">
-        <v>3.94</v>
+        <v>3.216</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.65</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3731</v>
+        <v>-0.3596</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.462</v>
+        <v>-7.192</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.55</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.462</v>
+        <v>-0.4566</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.24</v>
+        <v>-9.132</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6249</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.498</v>
+        <v>-12.872</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.56</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0368</v>
+        <v>1.0256</v>
       </c>
       <c r="J82" t="n">
-        <v>21.7728</v>
+        <v>21.5376</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.56</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0368</v>
+        <v>1.0256</v>
       </c>
       <c r="J83" t="n">
-        <v>21.7728</v>
+        <v>21.5376</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.12</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3599</v>
+        <v>0.3263</v>
       </c>
       <c r="J84" t="n">
-        <v>7.5579</v>
+        <v>6.8523</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0249</v>
+        <v>0.015</v>
       </c>
       <c r="J85" t="n">
-        <v>0.5229</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6495</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.6395</v>
+        <v>-12.9654</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.31</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6009</v>
+        <v>0.5784</v>
       </c>
       <c r="J87" t="n">
-        <v>12.6189</v>
+        <v>12.1464</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>0.86</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.18</v>
+        <v>-0.1615</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.78</v>
+        <v>-3.3915</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2105</v>
+        <v>-0.1912</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.4205</v>
+        <v>-4.0152</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2205</v>
+        <v>-0.2012</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.6305</v>
+        <v>-4.2252</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4781</v>
+        <v>-0.4753</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.0401</v>
+        <v>-9.981299999999999</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>0.91</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1109</v>
+        <v>-0.0963</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.9962</v>
+        <v>-1.7334</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.83</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2006</v>
+        <v>-0.1846</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.6108</v>
+        <v>-3.3228</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.75</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2775</v>
+        <v>-0.2613</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.995</v>
+        <v>-4.7034</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.68</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3413</v>
+        <v>-0.3265</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.1434</v>
+        <v>-5.877</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.63</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3865</v>
+        <v>-0.3741</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.957</v>
+        <v>-6.7338</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0356</v>
+        <v>1.0243</v>
       </c>
       <c r="J97" t="n">
-        <v>18.6408</v>
+        <v>18.4374</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7342</v>
+        <v>0.7215</v>
       </c>
       <c r="J98" t="n">
-        <v>13.2156</v>
+        <v>12.987</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.28</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6333</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>11.3994</v>
+        <v>11.241</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4777</v>
+        <v>0.4599</v>
       </c>
       <c r="J100" t="n">
-        <v>8.598599999999999</v>
+        <v>8.2782</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.0466</v>
+        <v>-0.0416</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.8388</v>
+        <v>-0.7488</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3704</v>
+        <v>0.3155</v>
       </c>
       <c r="J102" t="n">
-        <v>12.5936</v>
+        <v>10.727</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1523</v>
+        <v>0.1171</v>
       </c>
       <c r="J103" t="n">
-        <v>5.1782</v>
+        <v>3.9814</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0027</v>
+        <v>0.0013</v>
       </c>
       <c r="J104" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0442</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1558</v>
+        <v>-0.1361</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.2972</v>
+        <v>-4.6274</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.76</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2888</v>
+        <v>-0.2702</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.8192</v>
+        <v>-9.1868</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.44</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="J107" t="n">
-        <v>29.597</v>
+        <v>29.0802</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.43</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8565</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>29.121</v>
+        <v>28.6008</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.22</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5475</v>
+        <v>0.5409</v>
       </c>
       <c r="J109" t="n">
-        <v>18.615</v>
+        <v>18.3906</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.04</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1351</v>
+        <v>0.1115</v>
       </c>
       <c r="J110" t="n">
-        <v>4.5934</v>
+        <v>3.791</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2401</v>
+        <v>-0.2037</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.163399999999999</v>
+        <v>-6.9258</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7488</v>
+        <v>0.7327</v>
       </c>
       <c r="J112" t="n">
-        <v>17.2224</v>
+        <v>16.8521</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6098</v>
+        <v>0.5969</v>
       </c>
       <c r="J113" t="n">
-        <v>14.0254</v>
+        <v>13.7287</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.349</v>
+        <v>0.3111</v>
       </c>
       <c r="J114" t="n">
-        <v>8.026999999999999</v>
+        <v>7.1553</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.01</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0436</v>
+        <v>0.0326</v>
       </c>
       <c r="J115" t="n">
-        <v>1.0028</v>
+        <v>0.7498</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.8</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6079</v>
+        <v>-0.5708</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.9817</v>
+        <v>-13.1284</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.18</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4153</v>
+        <v>0.3599</v>
       </c>
       <c r="J117" t="n">
-        <v>9.5519</v>
+        <v>8.277699999999999</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.16</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3801</v>
+        <v>0.3253</v>
       </c>
       <c r="J118" t="n">
-        <v>8.7423</v>
+        <v>7.4819</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0542</v>
+        <v>-0.0435</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.2466</v>
+        <v>-1.0005</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2363</v>
+        <v>-0.2162</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.4349</v>
+        <v>-4.9726</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4751</v>
+        <v>-0.4726</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.9273</v>
+        <v>-10.8698</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.16</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2887</v>
+        <v>0.2758</v>
       </c>
       <c r="J122" t="n">
-        <v>6.3514</v>
+        <v>6.0676</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2457</v>
+        <v>0.2304</v>
       </c>
       <c r="J123" t="n">
-        <v>5.4054</v>
+        <v>5.0688</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.99</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0244</v>
+        <v>-0.0178</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.3916</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.93</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1099</v>
+        <v>-0.0925</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.4178</v>
+        <v>-2.035</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3551</v>
+        <v>-0.3407</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.8122</v>
+        <v>-7.4954</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.49</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5734</v>
+        <v>0.538</v>
       </c>
       <c r="J127" t="n">
-        <v>12.6148</v>
+        <v>11.836</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.2</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3013</v>
+        <v>0.2477</v>
       </c>
       <c r="J128" t="n">
-        <v>6.6286</v>
+        <v>5.4494</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.19</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2893</v>
+        <v>0.237</v>
       </c>
       <c r="J129" t="n">
-        <v>6.3646</v>
+        <v>5.214</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0406</v>
+        <v>0.0278</v>
       </c>
       <c r="J130" t="n">
-        <v>0.8932</v>
+        <v>0.6116</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.92</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1371</v>
+        <v>-0.1181</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.0162</v>
+        <v>-2.5982</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>2.22</v>
       </c>
       <c r="I132" t="n">
-        <v>1.7831</v>
+        <v>1.8315</v>
       </c>
       <c r="J132" t="n">
-        <v>28.5296</v>
+        <v>29.304</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.49</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.8966</v>
       </c>
       <c r="J133" t="n">
-        <v>14.4912</v>
+        <v>14.3456</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.48</v>
       </c>
       <c r="I134" t="n">
-        <v>0.8928</v>
+        <v>0.8838</v>
       </c>
       <c r="J134" t="n">
-        <v>14.2848</v>
+        <v>14.1408</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3706</v>
+        <v>0.3381</v>
       </c>
       <c r="J135" t="n">
-        <v>5.9296</v>
+        <v>5.4096</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2773</v>
+        <v>-0.2471</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.4368</v>
+        <v>-3.9536</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.26</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5703</v>
+        <v>0.5562</v>
       </c>
       <c r="J137" t="n">
-        <v>9.1248</v>
+        <v>8.8992</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1608</v>
+        <v>-0.145</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.5728</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.66</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.362</v>
+        <v>-0.3479</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.792</v>
+        <v>-5.5664</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.62</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.398</v>
+        <v>-0.3863</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.368</v>
+        <v>-6.1808</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5037</v>
+        <v>-0.5031</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.059200000000001</v>
+        <v>-8.0496</v>
       </c>
     </row>
   </sheetData>
